--- a/optimize_prep/output/curves_inspection.xlsx
+++ b/optimize_prep/output/curves_inspection.xlsx
@@ -1463,76 +1463,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.946861</v>
+        <v>0.94685</v>
       </c>
       <c r="D13" t="n">
-        <v>5.1929</v>
+        <v>5.2071</v>
       </c>
       <c r="E13" t="n">
-        <v>0.943846</v>
+        <v>0.943835</v>
       </c>
       <c r="F13" t="n">
-        <v>4.1274</v>
+        <v>4.1416</v>
       </c>
       <c r="G13" t="n">
-        <v>0.956377</v>
+        <v>0.956366</v>
       </c>
       <c r="H13" t="n">
-        <v>4.189</v>
+        <v>4.2032</v>
       </c>
       <c r="I13" t="n">
-        <v>0.956377</v>
+        <v>0.956366</v>
       </c>
       <c r="J13" t="n">
-        <v>4.189</v>
+        <v>4.2032</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9374400000000001</v>
+        <v>0.937428</v>
       </c>
       <c r="L13" t="n">
-        <v>6.1977</v>
+        <v>6.2119</v>
       </c>
       <c r="M13" t="n">
-        <v>0.946956</v>
+        <v>0.946944</v>
       </c>
       <c r="N13" t="n">
-        <v>5.1829</v>
+        <v>5.1971</v>
       </c>
       <c r="O13" t="n">
-        <v>0.946766</v>
+        <v>0.946755</v>
       </c>
       <c r="P13" t="n">
-        <v>5.203</v>
+        <v>5.2172</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.970831</v>
+        <v>0.970819</v>
       </c>
       <c r="R13" t="n">
-        <v>2.6847</v>
+        <v>2.6989</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9234830000000001</v>
+        <v>0.923472</v>
       </c>
       <c r="T13" t="n">
-        <v>7.7064</v>
+        <v>7.7206</v>
       </c>
       <c r="U13" t="n">
-        <v>0.959131</v>
+        <v>0.95912</v>
       </c>
       <c r="V13" t="n">
-        <v>5.136</v>
+        <v>5.1502</v>
       </c>
       <c r="W13" t="n">
-        <v>0.934748</v>
+        <v>0.934737</v>
       </c>
       <c r="X13" t="n">
-        <v>5.2499</v>
+        <v>5.2641</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.946705</v>
+        <v>0.946694</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.4905</v>
+        <v>6.5047</v>
       </c>
     </row>
     <row r="14">
@@ -1545,76 +1545,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.9251779999999999</v>
+        <v>0.923237</v>
       </c>
       <c r="D14" t="n">
-        <v>5.2035</v>
+        <v>5.3342</v>
       </c>
       <c r="E14" t="n">
-        <v>0.928643</v>
+        <v>0.926696</v>
       </c>
       <c r="F14" t="n">
-        <v>3.654</v>
+        <v>3.7845</v>
       </c>
       <c r="G14" t="n">
-        <v>0.93916</v>
+        <v>0.93719</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1996</v>
+        <v>4.3301</v>
       </c>
       <c r="I14" t="n">
-        <v>0.93916</v>
+        <v>0.93719</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1996</v>
+        <v>4.3301</v>
       </c>
       <c r="K14" t="n">
-        <v>0.911404</v>
+        <v>0.909492</v>
       </c>
       <c r="L14" t="n">
-        <v>6.2083</v>
+        <v>6.339</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9253169999999999</v>
+        <v>0.923376</v>
       </c>
       <c r="N14" t="n">
-        <v>5.1935</v>
+        <v>5.3241</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9250389999999999</v>
+        <v>0.923099</v>
       </c>
       <c r="P14" t="n">
-        <v>5.2136</v>
+        <v>5.3442</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.960531</v>
+        <v>0.958516</v>
       </c>
       <c r="R14" t="n">
-        <v>2.6953</v>
+        <v>2.8257</v>
       </c>
       <c r="S14" t="n">
-        <v>0.891126</v>
+        <v>0.889257</v>
       </c>
       <c r="T14" t="n">
-        <v>7.717</v>
+        <v>7.8479</v>
       </c>
       <c r="U14" t="n">
-        <v>0.936079</v>
+        <v>0.934115</v>
       </c>
       <c r="V14" t="n">
-        <v>5.5786</v>
+        <v>5.7093</v>
       </c>
       <c r="W14" t="n">
-        <v>0.914404</v>
+        <v>0.912486</v>
       </c>
       <c r="X14" t="n">
-        <v>4.8285</v>
+        <v>4.9591</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.917697</v>
+        <v>0.9157729999999999</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.9491</v>
+        <v>7.0799</v>
       </c>
     </row>
     <row r="15">
@@ -1627,76 +1627,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.901456</v>
+        <v>0.898998</v>
       </c>
       <c r="D15" t="n">
-        <v>5.2079</v>
+        <v>5.3321</v>
       </c>
       <c r="E15" t="n">
-        <v>0.912226</v>
+        <v>0.909738</v>
       </c>
       <c r="F15" t="n">
-        <v>3.5464</v>
+        <v>3.6704</v>
       </c>
       <c r="G15" t="n">
-        <v>0.919667</v>
+        <v>0.9171589999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>4.204</v>
+        <v>4.3281</v>
       </c>
       <c r="I15" t="n">
-        <v>0.919667</v>
+        <v>0.9171589999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>4.204</v>
+        <v>4.3281</v>
       </c>
       <c r="K15" t="n">
-        <v>0.883606</v>
+        <v>0.881196</v>
       </c>
       <c r="L15" t="n">
-        <v>6.2127</v>
+        <v>6.337</v>
       </c>
       <c r="M15" t="n">
-        <v>0.901637</v>
+        <v>0.899178</v>
       </c>
       <c r="N15" t="n">
-        <v>5.1979</v>
+        <v>5.3221</v>
       </c>
       <c r="O15" t="n">
-        <v>0.901276</v>
+        <v>0.898818</v>
       </c>
       <c r="P15" t="n">
-        <v>5.2179</v>
+        <v>5.3421</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.947675</v>
+        <v>0.94509</v>
       </c>
       <c r="R15" t="n">
-        <v>2.6997</v>
+        <v>2.8236</v>
       </c>
       <c r="S15" t="n">
-        <v>0.857492</v>
+        <v>0.8551530000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>7.7214</v>
+        <v>7.8458</v>
       </c>
       <c r="U15" t="n">
-        <v>0.910037</v>
+        <v>0.907555</v>
       </c>
       <c r="V15" t="n">
-        <v>5.6831</v>
+        <v>5.8073</v>
       </c>
       <c r="W15" t="n">
-        <v>0.892957</v>
+        <v>0.890521</v>
       </c>
       <c r="X15" t="n">
-        <v>4.7329</v>
+        <v>4.857</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.886094</v>
+        <v>0.883678</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.0573</v>
+        <v>7.1816</v>
       </c>
     </row>
     <row r="16">
@@ -1709,76 +1709,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.878325</v>
+        <v>0.875404</v>
       </c>
       <c r="D16" t="n">
-        <v>5.2118</v>
+        <v>5.3298</v>
       </c>
       <c r="E16" t="n">
-        <v>0.896131</v>
+        <v>0.893151</v>
       </c>
       <c r="F16" t="n">
-        <v>3.5912</v>
+        <v>3.7091</v>
       </c>
       <c r="G16" t="n">
-        <v>0.90056</v>
+        <v>0.8975649999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>4.2078</v>
+        <v>4.3258</v>
       </c>
       <c r="I16" t="n">
-        <v>0.90056</v>
+        <v>0.8975649999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>4.2078</v>
+        <v>4.3258</v>
       </c>
       <c r="K16" t="n">
-        <v>0.856639</v>
+        <v>0.85379</v>
       </c>
       <c r="L16" t="n">
-        <v>6.2165</v>
+        <v>6.3346</v>
       </c>
       <c r="M16" t="n">
-        <v>0.878545</v>
+        <v>0.875623</v>
       </c>
       <c r="N16" t="n">
-        <v>5.2017</v>
+        <v>5.3197</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8781060000000001</v>
+        <v>0.875185</v>
       </c>
       <c r="P16" t="n">
-        <v>5.2218</v>
+        <v>5.3398</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.934972</v>
+        <v>0.931863</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7035</v>
+        <v>2.8213</v>
       </c>
       <c r="S16" t="n">
-        <v>0.82511</v>
+        <v>0.822366</v>
       </c>
       <c r="T16" t="n">
-        <v>7.7252</v>
+        <v>7.8435</v>
       </c>
       <c r="U16" t="n">
-        <v>0.884657</v>
+        <v>0.881715</v>
       </c>
       <c r="V16" t="n">
-        <v>5.6504</v>
+        <v>5.7684</v>
       </c>
       <c r="W16" t="n">
-        <v>0.872039</v>
+        <v>0.869139</v>
       </c>
       <c r="X16" t="n">
-        <v>4.7733</v>
+        <v>4.8913</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.855517</v>
+        <v>0.852672</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.0232</v>
+        <v>7.1413</v>
       </c>
     </row>
     <row r="17">
@@ -1791,76 +1791,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.855773</v>
+        <v>0.85244</v>
       </c>
       <c r="D17" t="n">
-        <v>5.2151</v>
+        <v>5.3273</v>
       </c>
       <c r="E17" t="n">
-        <v>0.879974</v>
+        <v>0.876547</v>
       </c>
       <c r="F17" t="n">
-        <v>3.6853</v>
+        <v>3.7974</v>
       </c>
       <c r="G17" t="n">
-        <v>0.881835</v>
+        <v>0.878401</v>
       </c>
       <c r="H17" t="n">
-        <v>4.2112</v>
+        <v>4.3232</v>
       </c>
       <c r="I17" t="n">
-        <v>0.881835</v>
+        <v>0.878401</v>
       </c>
       <c r="J17" t="n">
-        <v>4.2112</v>
+        <v>4.3232</v>
       </c>
       <c r="K17" t="n">
-        <v>0.830481</v>
+        <v>0.827247</v>
       </c>
       <c r="L17" t="n">
-        <v>6.2199</v>
+        <v>6.3321</v>
       </c>
       <c r="M17" t="n">
-        <v>0.856029</v>
+        <v>0.852696</v>
       </c>
       <c r="N17" t="n">
-        <v>5.2051</v>
+        <v>5.3172</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8555160000000001</v>
+        <v>0.852185</v>
       </c>
       <c r="P17" t="n">
-        <v>5.2251</v>
+        <v>5.3373</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.922424</v>
+        <v>0.918832</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7069</v>
+        <v>2.8188</v>
       </c>
       <c r="S17" t="n">
-        <v>0.793937</v>
+        <v>0.790846</v>
       </c>
       <c r="T17" t="n">
-        <v>7.7286</v>
+        <v>7.841</v>
       </c>
       <c r="U17" t="n">
-        <v>0.860258</v>
+        <v>0.856908</v>
       </c>
       <c r="V17" t="n">
-        <v>5.5726</v>
+        <v>5.6848</v>
       </c>
       <c r="W17" t="n">
-        <v>0.85131</v>
+        <v>0.847996</v>
       </c>
       <c r="X17" t="n">
-        <v>4.8577</v>
+        <v>4.9698</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.826268</v>
+        <v>0.823051</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.9424</v>
+        <v>7.0547</v>
       </c>
     </row>
     <row r="18">
@@ -1873,76 +1873,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.833786</v>
+        <v>0.83009</v>
       </c>
       <c r="D18" t="n">
-        <v>5.218</v>
+        <v>5.3246</v>
       </c>
       <c r="E18" t="n">
-        <v>0.863681</v>
+        <v>0.8598519999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>3.784</v>
+        <v>3.8904</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8634849999999999</v>
+        <v>0.859657</v>
       </c>
       <c r="H18" t="n">
-        <v>4.2141</v>
+        <v>4.3205</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8634849999999999</v>
+        <v>0.859657</v>
       </c>
       <c r="J18" t="n">
-        <v>4.2141</v>
+        <v>4.3205</v>
       </c>
       <c r="K18" t="n">
-        <v>0.805108</v>
+        <v>0.801539</v>
       </c>
       <c r="L18" t="n">
-        <v>6.2228</v>
+        <v>6.3294</v>
       </c>
       <c r="M18" t="n">
-        <v>0.834078</v>
+        <v>0.83038</v>
       </c>
       <c r="N18" t="n">
-        <v>5.208</v>
+        <v>5.3145</v>
       </c>
       <c r="O18" t="n">
-        <v>0.833494</v>
+        <v>0.829799</v>
       </c>
       <c r="P18" t="n">
-        <v>5.2281</v>
+        <v>5.3346</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.910029</v>
+        <v>0.905995</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7097</v>
+        <v>2.8161</v>
       </c>
       <c r="S18" t="n">
-        <v>0.763931</v>
+        <v>0.760544</v>
       </c>
       <c r="T18" t="n">
-        <v>7.7315</v>
+        <v>7.8383</v>
       </c>
       <c r="U18" t="n">
-        <v>0.836876</v>
+        <v>0.833166</v>
       </c>
       <c r="V18" t="n">
-        <v>5.49</v>
+        <v>5.5966</v>
       </c>
       <c r="W18" t="n">
-        <v>0.830707</v>
+        <v>0.827024</v>
       </c>
       <c r="X18" t="n">
-        <v>4.946</v>
+        <v>5.0526</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.798359</v>
+        <v>0.79482</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.8567</v>
+        <v>6.9634</v>
       </c>
     </row>
     <row r="19">
@@ -1955,76 +1955,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.812354</v>
+        <v>0.8083360000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>5.2205</v>
+        <v>5.3217</v>
       </c>
       <c r="E19" t="n">
-        <v>0.847305</v>
+        <v>0.843114</v>
       </c>
       <c r="F19" t="n">
-        <v>3.869</v>
+        <v>3.9701</v>
       </c>
       <c r="G19" t="n">
-        <v>0.845507</v>
+        <v>0.841325</v>
       </c>
       <c r="H19" t="n">
-        <v>4.2166</v>
+        <v>4.3177</v>
       </c>
       <c r="I19" t="n">
-        <v>0.845507</v>
+        <v>0.841325</v>
       </c>
       <c r="J19" t="n">
-        <v>4.2166</v>
+        <v>4.3177</v>
       </c>
       <c r="K19" t="n">
-        <v>0.780501</v>
+        <v>0.776641</v>
       </c>
       <c r="L19" t="n">
-        <v>6.2253</v>
+        <v>6.3266</v>
       </c>
       <c r="M19" t="n">
-        <v>0.812679</v>
+        <v>0.808659</v>
       </c>
       <c r="N19" t="n">
-        <v>5.2104</v>
+        <v>5.3117</v>
       </c>
       <c r="O19" t="n">
-        <v>0.812029</v>
+        <v>0.808013</v>
       </c>
       <c r="P19" t="n">
-        <v>5.2305</v>
+        <v>5.3318</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.89779</v>
+        <v>0.8933489999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>2.7122</v>
+        <v>2.8133</v>
       </c>
       <c r="S19" t="n">
-        <v>0.735048</v>
+        <v>0.731413</v>
       </c>
       <c r="T19" t="n">
-        <v>7.734</v>
+        <v>7.8354</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8144400000000001</v>
+        <v>0.810412</v>
       </c>
       <c r="V19" t="n">
-        <v>5.4188</v>
+        <v>5.5201</v>
       </c>
       <c r="W19" t="n">
-        <v>0.810273</v>
+        <v>0.806266</v>
       </c>
       <c r="X19" t="n">
-        <v>5.0222</v>
+        <v>5.1234</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.771697</v>
+        <v>0.76788</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.7828</v>
+        <v>6.8842</v>
       </c>
     </row>
     <row r="20">
@@ -2037,76 +2037,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.7914639999999999</v>
+        <v>0.787164</v>
       </c>
       <c r="D20" t="n">
-        <v>5.2226</v>
+        <v>5.3188</v>
       </c>
       <c r="E20" t="n">
-        <v>0.830931</v>
+        <v>0.826417</v>
       </c>
       <c r="F20" t="n">
-        <v>3.9355</v>
+        <v>4.0316</v>
       </c>
       <c r="G20" t="n">
-        <v>0.827893</v>
+        <v>0.823395</v>
       </c>
       <c r="H20" t="n">
-        <v>4.2187</v>
+        <v>4.3148</v>
       </c>
       <c r="I20" t="n">
-        <v>0.827893</v>
+        <v>0.823395</v>
       </c>
       <c r="J20" t="n">
-        <v>4.2187</v>
+        <v>4.3148</v>
       </c>
       <c r="K20" t="n">
-        <v>0.756637</v>
+        <v>0.7525269999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>6.2274</v>
+        <v>6.3237</v>
       </c>
       <c r="M20" t="n">
-        <v>0.79182</v>
+        <v>0.7875180000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>5.2126</v>
+        <v>5.3088</v>
       </c>
       <c r="O20" t="n">
-        <v>0.791108</v>
+        <v>0.78681</v>
       </c>
       <c r="P20" t="n">
-        <v>5.2327</v>
+        <v>5.3289</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.885705</v>
+        <v>0.880893</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7144</v>
+        <v>2.8104</v>
       </c>
       <c r="S20" t="n">
-        <v>0.70725</v>
+        <v>0.703407</v>
       </c>
       <c r="T20" t="n">
-        <v>7.7361</v>
+        <v>7.8325</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7928500000000001</v>
+        <v>0.788542</v>
       </c>
       <c r="V20" t="n">
-        <v>5.3634</v>
+        <v>5.4596</v>
       </c>
       <c r="W20" t="n">
-        <v>0.79008</v>
+        <v>0.785788</v>
       </c>
       <c r="X20" t="n">
-        <v>5.0818</v>
+        <v>5.178</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.746165</v>
+        <v>0.742111</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.7252</v>
+        <v>6.8216</v>
       </c>
     </row>
     <row r="21">
@@ -2119,76 +2119,76 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.771103</v>
+        <v>0.766557</v>
       </c>
       <c r="D21" t="n">
-        <v>5.2244</v>
+        <v>5.3159</v>
       </c>
       <c r="E21" t="n">
-        <v>0.814643</v>
+        <v>0.80984</v>
       </c>
       <c r="F21" t="n">
-        <v>3.9855</v>
+        <v>4.0768</v>
       </c>
       <c r="G21" t="n">
-        <v>0.810639</v>
+        <v>0.80586</v>
       </c>
       <c r="H21" t="n">
-        <v>4.2205</v>
+        <v>4.3118</v>
       </c>
       <c r="I21" t="n">
-        <v>0.810639</v>
+        <v>0.80586</v>
       </c>
       <c r="J21" t="n">
-        <v>4.2205</v>
+        <v>4.3118</v>
       </c>
       <c r="K21" t="n">
-        <v>0.733496</v>
+        <v>0.729172</v>
       </c>
       <c r="L21" t="n">
-        <v>6.2292</v>
+        <v>6.3207</v>
       </c>
       <c r="M21" t="n">
-        <v>0.771489</v>
+        <v>0.766941</v>
       </c>
       <c r="N21" t="n">
-        <v>5.2144</v>
+        <v>5.3058</v>
       </c>
       <c r="O21" t="n">
-        <v>0.770718</v>
+        <v>0.766174</v>
       </c>
       <c r="P21" t="n">
-        <v>5.2345</v>
+        <v>5.3259</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.8737740000000001</v>
+        <v>0.868623</v>
       </c>
       <c r="R21" t="n">
-        <v>2.7162</v>
+        <v>2.8074</v>
       </c>
       <c r="S21" t="n">
-        <v>0.680496</v>
+        <v>0.676484</v>
       </c>
       <c r="T21" t="n">
-        <v>7.7379</v>
+        <v>7.8296</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7720129999999999</v>
+        <v>0.767462</v>
       </c>
       <c r="V21" t="n">
-        <v>5.3223</v>
+        <v>5.4137</v>
       </c>
       <c r="W21" t="n">
-        <v>0.770194</v>
+        <v>0.7656539999999999</v>
       </c>
       <c r="X21" t="n">
-        <v>5.1266</v>
+        <v>5.218</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.721652</v>
+        <v>0.717398</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.6825</v>
+        <v>6.774</v>
       </c>
     </row>
     <row r="22">
@@ -2201,76 +2201,76 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.731923</v>
+        <v>0.726982</v>
       </c>
       <c r="D22" t="n">
-        <v>5.2272</v>
+        <v>5.3098</v>
       </c>
       <c r="E22" t="n">
-        <v>0.782576</v>
+        <v>0.777293</v>
       </c>
       <c r="F22" t="n">
-        <v>4.0474</v>
+        <v>4.1298</v>
       </c>
       <c r="G22" t="n">
-        <v>0.777183</v>
+        <v>0.771936</v>
       </c>
       <c r="H22" t="n">
-        <v>4.2233</v>
+        <v>4.3058</v>
       </c>
       <c r="I22" t="n">
-        <v>0.777183</v>
+        <v>0.771936</v>
       </c>
       <c r="J22" t="n">
-        <v>4.2233</v>
+        <v>4.3058</v>
       </c>
       <c r="K22" t="n">
-        <v>0.689299</v>
+        <v>0.6846449999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>6.232</v>
+        <v>6.3146</v>
       </c>
       <c r="M22" t="n">
-        <v>0.732362</v>
+        <v>0.727418</v>
       </c>
       <c r="N22" t="n">
-        <v>5.2172</v>
+        <v>5.2997</v>
       </c>
       <c r="O22" t="n">
-        <v>0.731484</v>
+        <v>0.726545</v>
       </c>
       <c r="P22" t="n">
-        <v>5.2373</v>
+        <v>5.3198</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.850373</v>
+        <v>0.844632</v>
       </c>
       <c r="R22" t="n">
-        <v>2.719</v>
+        <v>2.8013</v>
       </c>
       <c r="S22" t="n">
-        <v>0.629972</v>
+        <v>0.625719</v>
       </c>
       <c r="T22" t="n">
-        <v>7.7407</v>
+        <v>7.8235</v>
       </c>
       <c r="U22" t="n">
-        <v>0.732304</v>
+        <v>0.72736</v>
       </c>
       <c r="V22" t="n">
-        <v>5.2723</v>
+        <v>5.3549</v>
       </c>
       <c r="W22" t="n">
-        <v>0.731542</v>
+        <v>0.726603</v>
       </c>
       <c r="X22" t="n">
-        <v>5.1822</v>
+        <v>5.2647</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.675339</v>
+        <v>0.670779</v>
       </c>
       <c r="Z22" t="n">
-        <v>6.6306</v>
+        <v>6.7133</v>
       </c>
     </row>
     <row r="23">
@@ -2283,76 +2283,76 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.6947179999999999</v>
+        <v>0.689491</v>
       </c>
       <c r="D23" t="n">
-        <v>5.2292</v>
+        <v>5.3037</v>
       </c>
       <c r="E23" t="n">
-        <v>0.75145</v>
+        <v>0.745797</v>
       </c>
       <c r="F23" t="n">
-        <v>4.0775</v>
+        <v>4.1519</v>
       </c>
       <c r="G23" t="n">
-        <v>0.74509</v>
+        <v>0.7394849999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>4.2252</v>
+        <v>4.2997</v>
       </c>
       <c r="I23" t="n">
-        <v>0.74509</v>
+        <v>0.7394849999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>4.2252</v>
+        <v>4.2997</v>
       </c>
       <c r="K23" t="n">
-        <v>0.64775</v>
+        <v>0.642877</v>
       </c>
       <c r="L23" t="n">
-        <v>6.2339</v>
+        <v>6.3085</v>
       </c>
       <c r="M23" t="n">
-        <v>0.695204</v>
+        <v>0.689974</v>
       </c>
       <c r="N23" t="n">
-        <v>5.2191</v>
+        <v>5.2936</v>
       </c>
       <c r="O23" t="n">
-        <v>0.694231</v>
+        <v>0.689008</v>
       </c>
       <c r="P23" t="n">
-        <v>5.2392</v>
+        <v>5.3137</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.82758</v>
+        <v>0.821353</v>
       </c>
       <c r="R23" t="n">
-        <v>2.7209</v>
+        <v>2.7952</v>
       </c>
       <c r="S23" t="n">
-        <v>0.583186</v>
+        <v>0.578798</v>
       </c>
       <c r="T23" t="n">
-        <v>7.7427</v>
+        <v>7.8173</v>
       </c>
       <c r="U23" t="n">
-        <v>0.694873</v>
+        <v>0.689645</v>
       </c>
       <c r="V23" t="n">
-        <v>5.2491</v>
+        <v>5.3236</v>
       </c>
       <c r="W23" t="n">
-        <v>0.694562</v>
+        <v>0.689337</v>
       </c>
       <c r="X23" t="n">
-        <v>5.2093</v>
+        <v>5.2838</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.63222</v>
+        <v>0.627463</v>
       </c>
       <c r="Z23" t="n">
-        <v>6.6065</v>
+        <v>6.681</v>
       </c>
     </row>
     <row r="24">
@@ -2365,76 +2365,76 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.659393</v>
+        <v>0.653973</v>
       </c>
       <c r="D24" t="n">
-        <v>5.2304</v>
+        <v>5.2977</v>
       </c>
       <c r="E24" t="n">
-        <v>0.721415</v>
+        <v>0.715485</v>
       </c>
       <c r="F24" t="n">
-        <v>4.0914</v>
+        <v>4.1586</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7143119999999999</v>
+        <v>0.708441</v>
       </c>
       <c r="H24" t="n">
-        <v>4.2265</v>
+        <v>4.2937</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7143119999999999</v>
+        <v>0.708441</v>
       </c>
       <c r="J24" t="n">
-        <v>4.2265</v>
+        <v>4.2937</v>
       </c>
       <c r="K24" t="n">
-        <v>0.608697</v>
+        <v>0.603693</v>
       </c>
       <c r="L24" t="n">
-        <v>6.2352</v>
+        <v>6.3025</v>
       </c>
       <c r="M24" t="n">
-        <v>0.659921</v>
+        <v>0.654496</v>
       </c>
       <c r="N24" t="n">
-        <v>5.2204</v>
+        <v>5.2876</v>
       </c>
       <c r="O24" t="n">
-        <v>0.658866</v>
+        <v>0.65345</v>
       </c>
       <c r="P24" t="n">
-        <v>5.2405</v>
+        <v>5.3077</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.805385</v>
+        <v>0.798764</v>
       </c>
       <c r="R24" t="n">
-        <v>2.7221</v>
+        <v>2.7892</v>
       </c>
       <c r="S24" t="n">
-        <v>0.539866</v>
+        <v>0.535428</v>
       </c>
       <c r="T24" t="n">
-        <v>7.7439</v>
+        <v>7.8113</v>
       </c>
       <c r="U24" t="n">
-        <v>0.659455</v>
+        <v>0.654034</v>
       </c>
       <c r="V24" t="n">
-        <v>5.239</v>
+        <v>5.3062</v>
       </c>
       <c r="W24" t="n">
-        <v>0.659331</v>
+        <v>0.653912</v>
       </c>
       <c r="X24" t="n">
-        <v>5.2219</v>
+        <v>5.2891</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.591947</v>
+        <v>0.587081</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.5959</v>
+        <v>6.6632</v>
       </c>
     </row>
     <row r="25">
@@ -2447,76 +2447,76 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.6258590000000001</v>
+        <v>0.620322</v>
       </c>
       <c r="D25" t="n">
-        <v>5.2311</v>
+        <v>5.2918</v>
       </c>
       <c r="E25" t="n">
-        <v>0.692516</v>
+        <v>0.686389</v>
       </c>
       <c r="F25" t="n">
-        <v>4.0977</v>
+        <v>4.1583</v>
       </c>
       <c r="G25" t="n">
-        <v>0.684799</v>
+        <v>0.67874</v>
       </c>
       <c r="H25" t="n">
-        <v>4.2272</v>
+        <v>4.2878</v>
       </c>
       <c r="I25" t="n">
-        <v>0.684799</v>
+        <v>0.67874</v>
       </c>
       <c r="J25" t="n">
-        <v>4.2272</v>
+        <v>4.2878</v>
       </c>
       <c r="K25" t="n">
-        <v>0.5719919999999999</v>
+        <v>0.566931</v>
       </c>
       <c r="L25" t="n">
-        <v>6.2359</v>
+        <v>6.2966</v>
       </c>
       <c r="M25" t="n">
-        <v>0.626423</v>
+        <v>0.62088</v>
       </c>
       <c r="N25" t="n">
-        <v>5.2211</v>
+        <v>5.2817</v>
       </c>
       <c r="O25" t="n">
-        <v>0.625296</v>
+        <v>0.619763</v>
       </c>
       <c r="P25" t="n">
-        <v>5.2412</v>
+        <v>5.3018</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.783778</v>
+        <v>0.776843</v>
       </c>
       <c r="R25" t="n">
-        <v>2.7228</v>
+        <v>2.7834</v>
       </c>
       <c r="S25" t="n">
-        <v>0.499759</v>
+        <v>0.495337</v>
       </c>
       <c r="T25" t="n">
-        <v>7.7446</v>
+        <v>7.8054</v>
       </c>
       <c r="U25" t="n">
-        <v>0.625884</v>
+        <v>0.620346</v>
       </c>
       <c r="V25" t="n">
-        <v>5.2347</v>
+        <v>5.2954</v>
       </c>
       <c r="W25" t="n">
-        <v>0.625835</v>
+        <v>0.620297</v>
       </c>
       <c r="X25" t="n">
-        <v>5.2275</v>
+        <v>5.2882</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.554278</v>
+        <v>0.549373</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.5915</v>
+        <v>6.6522</v>
       </c>
     </row>
     <row r="26">
@@ -2529,76 +2529,76 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.594028</v>
+        <v>0.588435</v>
       </c>
       <c r="D26" t="n">
-        <v>5.2314</v>
+        <v>5.2862</v>
       </c>
       <c r="E26" t="n">
-        <v>0.664748</v>
+        <v>0.65849</v>
       </c>
       <c r="F26" t="n">
-        <v>4.1004</v>
+        <v>4.1551</v>
       </c>
       <c r="G26" t="n">
-        <v>0.656502</v>
+        <v>0.650321</v>
       </c>
       <c r="H26" t="n">
-        <v>4.2275</v>
+        <v>4.2822</v>
       </c>
       <c r="I26" t="n">
-        <v>0.656502</v>
+        <v>0.650321</v>
       </c>
       <c r="J26" t="n">
-        <v>4.2275</v>
+        <v>4.2822</v>
       </c>
       <c r="K26" t="n">
-        <v>0.5374989999999999</v>
+        <v>0.532438</v>
       </c>
       <c r="L26" t="n">
-        <v>6.2362</v>
+        <v>6.291</v>
       </c>
       <c r="M26" t="n">
-        <v>0.594622</v>
+        <v>0.589024</v>
       </c>
       <c r="N26" t="n">
-        <v>5.2214</v>
+        <v>5.2761</v>
       </c>
       <c r="O26" t="n">
-        <v>0.593434</v>
+        <v>0.587847</v>
       </c>
       <c r="P26" t="n">
-        <v>5.2415</v>
+        <v>5.2962</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.762747</v>
+        <v>0.755566</v>
       </c>
       <c r="R26" t="n">
-        <v>2.7231</v>
+        <v>2.7778</v>
       </c>
       <c r="S26" t="n">
-        <v>0.462629</v>
+        <v>0.458274</v>
       </c>
       <c r="T26" t="n">
-        <v>7.745</v>
+        <v>7.7998</v>
       </c>
       <c r="U26" t="n">
-        <v>0.594037</v>
+        <v>0.588445</v>
       </c>
       <c r="V26" t="n">
-        <v>5.2329</v>
+        <v>5.2877</v>
       </c>
       <c r="W26" t="n">
-        <v>0.594018</v>
+        <v>0.588426</v>
       </c>
       <c r="X26" t="n">
-        <v>5.2299</v>
+        <v>5.2847</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.51902</v>
+        <v>0.514134</v>
       </c>
       <c r="Z26" t="n">
-        <v>6.5896</v>
+        <v>6.6444</v>
       </c>
     </row>
     <row r="27">
@@ -2611,76 +2611,76 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.45758</v>
+        <v>0.452312</v>
       </c>
       <c r="D27" t="n">
-        <v>5.2298</v>
+        <v>5.2624</v>
       </c>
       <c r="E27" t="n">
-        <v>0.541694</v>
+        <v>0.535458</v>
       </c>
       <c r="F27" t="n">
-        <v>4.1004</v>
+        <v>4.133</v>
       </c>
       <c r="G27" t="n">
-        <v>0.531632</v>
+        <v>0.525512</v>
       </c>
       <c r="H27" t="n">
-        <v>4.2258</v>
+        <v>4.2584</v>
       </c>
       <c r="I27" t="n">
-        <v>0.531632</v>
+        <v>0.525512</v>
       </c>
       <c r="J27" t="n">
-        <v>4.2258</v>
+        <v>4.2584</v>
       </c>
       <c r="K27" t="n">
-        <v>0.393842</v>
+        <v>0.389309</v>
       </c>
       <c r="L27" t="n">
-        <v>6.2345</v>
+        <v>6.2672</v>
       </c>
       <c r="M27" t="n">
-        <v>0.458267</v>
+        <v>0.452991</v>
       </c>
       <c r="N27" t="n">
-        <v>5.2197</v>
+        <v>5.2523</v>
       </c>
       <c r="O27" t="n">
-        <v>0.456894</v>
+        <v>0.451634</v>
       </c>
       <c r="P27" t="n">
-        <v>5.2398</v>
+        <v>5.2724</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.665775</v>
+        <v>0.65811</v>
       </c>
       <c r="R27" t="n">
-        <v>2.7215</v>
+        <v>2.754</v>
       </c>
       <c r="S27" t="n">
-        <v>0.31449</v>
+        <v>0.310869</v>
       </c>
       <c r="T27" t="n">
-        <v>7.7432</v>
+        <v>7.776</v>
       </c>
       <c r="U27" t="n">
-        <v>0.45758</v>
+        <v>0.452312</v>
       </c>
       <c r="V27" t="n">
-        <v>5.2298</v>
+        <v>5.2624</v>
       </c>
       <c r="W27" t="n">
-        <v>0.45758</v>
+        <v>0.452312</v>
       </c>
       <c r="X27" t="n">
-        <v>5.2297</v>
+        <v>5.2624</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.373699</v>
+        <v>0.369397</v>
       </c>
       <c r="Z27" t="n">
-        <v>6.5864</v>
+        <v>6.6191</v>
       </c>
     </row>
     <row r="28">
@@ -2693,76 +2693,76 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.352522</v>
+        <v>0.348024</v>
       </c>
       <c r="D28" t="n">
-        <v>5.2266</v>
+        <v>5.2459</v>
       </c>
       <c r="E28" t="n">
-        <v>0.441471</v>
+        <v>0.435839</v>
       </c>
       <c r="F28" t="n">
-        <v>4.0972</v>
+        <v>4.1165</v>
       </c>
       <c r="G28" t="n">
-        <v>0.430571</v>
+        <v>0.425078</v>
       </c>
       <c r="H28" t="n">
-        <v>4.2226</v>
+        <v>4.242</v>
       </c>
       <c r="I28" t="n">
-        <v>0.430571</v>
+        <v>0.425078</v>
       </c>
       <c r="J28" t="n">
-        <v>4.2226</v>
+        <v>4.242</v>
       </c>
       <c r="K28" t="n">
-        <v>0.28862</v>
+        <v>0.284938</v>
       </c>
       <c r="L28" t="n">
-        <v>6.2314</v>
+        <v>6.2507</v>
       </c>
       <c r="M28" t="n">
-        <v>0.353228</v>
+        <v>0.348721</v>
       </c>
       <c r="N28" t="n">
-        <v>5.2165</v>
+        <v>5.2359</v>
       </c>
       <c r="O28" t="n">
-        <v>0.351817</v>
+        <v>0.347329</v>
       </c>
       <c r="P28" t="n">
-        <v>5.2366</v>
+        <v>5.2559</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.58121</v>
+        <v>0.5737950000000001</v>
       </c>
       <c r="R28" t="n">
-        <v>2.7183</v>
+        <v>2.7376</v>
       </c>
       <c r="S28" t="n">
-        <v>0.213815</v>
+        <v>0.211087</v>
       </c>
       <c r="T28" t="n">
-        <v>7.7401</v>
+        <v>7.7595</v>
       </c>
       <c r="U28" t="n">
-        <v>0.352522</v>
+        <v>0.348024</v>
       </c>
       <c r="V28" t="n">
-        <v>5.2266</v>
+        <v>5.2459</v>
       </c>
       <c r="W28" t="n">
-        <v>0.352522</v>
+        <v>0.348024</v>
       </c>
       <c r="X28" t="n">
-        <v>5.2266</v>
+        <v>5.2459</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.269108</v>
+        <v>0.265675</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.5832</v>
+        <v>6.6026</v>
       </c>
     </row>
     <row r="29">
@@ -2775,76 +2775,76 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.271625</v>
+        <v>0.26796</v>
       </c>
       <c r="D29" t="n">
-        <v>5.2239</v>
+        <v>5.2352</v>
       </c>
       <c r="E29" t="n">
-        <v>0.359845</v>
+        <v>0.35499</v>
       </c>
       <c r="F29" t="n">
-        <v>4.0945</v>
+        <v>4.1059</v>
       </c>
       <c r="G29" t="n">
-        <v>0.348774</v>
+        <v>0.344068</v>
       </c>
       <c r="H29" t="n">
-        <v>4.22</v>
+        <v>4.2313</v>
       </c>
       <c r="I29" t="n">
-        <v>0.348774</v>
+        <v>0.344068</v>
       </c>
       <c r="J29" t="n">
-        <v>4.22</v>
+        <v>4.2313</v>
       </c>
       <c r="K29" t="n">
-        <v>0.211542</v>
+        <v>0.208688</v>
       </c>
       <c r="L29" t="n">
-        <v>6.2286</v>
+        <v>6.24</v>
       </c>
       <c r="M29" t="n">
-        <v>0.272305</v>
+        <v>0.268631</v>
       </c>
       <c r="N29" t="n">
-        <v>5.2138</v>
+        <v>5.2252</v>
       </c>
       <c r="O29" t="n">
-        <v>0.270947</v>
+        <v>0.267291</v>
       </c>
       <c r="P29" t="n">
-        <v>5.2339</v>
+        <v>5.2453</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.507463</v>
+        <v>0.5006159999999999</v>
       </c>
       <c r="R29" t="n">
-        <v>2.7156</v>
+        <v>2.727</v>
       </c>
       <c r="S29" t="n">
-        <v>0.14539</v>
+        <v>0.143429</v>
       </c>
       <c r="T29" t="n">
-        <v>7.7374</v>
+        <v>7.7487</v>
       </c>
       <c r="U29" t="n">
-        <v>0.271625</v>
+        <v>0.26796</v>
       </c>
       <c r="V29" t="n">
-        <v>5.2239</v>
+        <v>5.2352</v>
       </c>
       <c r="W29" t="n">
-        <v>0.271625</v>
+        <v>0.26796</v>
       </c>
       <c r="X29" t="n">
-        <v>5.2239</v>
+        <v>5.2352</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.193819</v>
+        <v>0.191204</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.5805</v>
+        <v>6.5919</v>
       </c>
     </row>
     <row r="30">
@@ -2857,76 +2857,76 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.209332</v>
+        <v>0.206417</v>
       </c>
       <c r="D30" t="n">
-        <v>5.136</v>
+        <v>5.1425</v>
       </c>
       <c r="E30" t="n">
-        <v>0.293361</v>
+        <v>0.289277</v>
       </c>
       <c r="F30" t="n">
-        <v>4.0252</v>
+        <v>4.0317</v>
       </c>
       <c r="G30" t="n">
-        <v>0.282564</v>
+        <v>0.27863</v>
       </c>
       <c r="H30" t="n">
-        <v>4.1486</v>
+        <v>4.1551</v>
       </c>
       <c r="I30" t="n">
-        <v>0.282564</v>
+        <v>0.27863</v>
       </c>
       <c r="J30" t="n">
-        <v>4.1486</v>
+        <v>4.1551</v>
       </c>
       <c r="K30" t="n">
-        <v>0.155079</v>
+        <v>0.15292</v>
       </c>
       <c r="L30" t="n">
-        <v>6.1241</v>
+        <v>6.1307</v>
       </c>
       <c r="M30" t="n">
-        <v>0.20996</v>
+        <v>0.207037</v>
       </c>
       <c r="N30" t="n">
-        <v>5.1262</v>
+        <v>5.1326</v>
       </c>
       <c r="O30" t="n">
-        <v>0.208705</v>
+        <v>0.205799</v>
       </c>
       <c r="P30" t="n">
-        <v>5.1458</v>
+        <v>5.1524</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.44314</v>
+        <v>0.43697</v>
       </c>
       <c r="R30" t="n">
-        <v>2.6691</v>
+        <v>2.6756</v>
       </c>
       <c r="S30" t="n">
-        <v>0.098885</v>
+        <v>0.097508</v>
       </c>
       <c r="T30" t="n">
-        <v>7.608</v>
+        <v>7.6145</v>
       </c>
       <c r="U30" t="n">
-        <v>0.209332</v>
+        <v>0.206417</v>
       </c>
       <c r="V30" t="n">
-        <v>5.136</v>
+        <v>5.1425</v>
       </c>
       <c r="W30" t="n">
-        <v>0.209332</v>
+        <v>0.206417</v>
       </c>
       <c r="X30" t="n">
-        <v>5.136</v>
+        <v>5.1425</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.139622</v>
+        <v>0.137678</v>
       </c>
       <c r="Z30" t="n">
-        <v>6.4702</v>
+        <v>6.4767</v>
       </c>
     </row>
   </sheetData>
@@ -8542,40 +8542,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5.1929</v>
+        <v>5.2071</v>
       </c>
       <c r="E11" t="n">
-        <v>4.1274</v>
+        <v>4.1416</v>
       </c>
       <c r="F11" t="n">
-        <v>4.189</v>
+        <v>4.2032</v>
       </c>
       <c r="G11" t="n">
-        <v>4.189</v>
+        <v>4.2032</v>
       </c>
       <c r="H11" t="n">
-        <v>6.1977</v>
+        <v>6.2119</v>
       </c>
       <c r="I11" t="n">
-        <v>5.1829</v>
+        <v>5.1971</v>
       </c>
       <c r="J11" t="n">
-        <v>5.203</v>
+        <v>5.2172</v>
       </c>
       <c r="K11" t="n">
-        <v>2.6847</v>
+        <v>2.6989</v>
       </c>
       <c r="L11" t="n">
-        <v>7.7064</v>
+        <v>7.7206</v>
       </c>
       <c r="M11" t="n">
-        <v>5.136</v>
+        <v>5.1502</v>
       </c>
       <c r="N11" t="n">
-        <v>5.2499</v>
+        <v>5.2641</v>
       </c>
       <c r="O11" t="n">
-        <v>6.4905</v>
+        <v>6.5047</v>
       </c>
     </row>
     <row r="12">
@@ -8695,40 +8695,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5.2079</v>
+        <v>5.3321</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5464</v>
+        <v>3.6704</v>
       </c>
       <c r="F14" t="n">
-        <v>4.204</v>
+        <v>4.3281</v>
       </c>
       <c r="G14" t="n">
-        <v>4.204</v>
+        <v>4.3281</v>
       </c>
       <c r="H14" t="n">
-        <v>6.2127</v>
+        <v>6.337</v>
       </c>
       <c r="I14" t="n">
-        <v>5.1979</v>
+        <v>5.3221</v>
       </c>
       <c r="J14" t="n">
-        <v>5.2179</v>
+        <v>5.3421</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6997</v>
+        <v>2.8236</v>
       </c>
       <c r="L14" t="n">
-        <v>7.7214</v>
+        <v>7.8458</v>
       </c>
       <c r="M14" t="n">
-        <v>5.6831</v>
+        <v>5.8073</v>
       </c>
       <c r="N14" t="n">
-        <v>4.7329</v>
+        <v>4.857</v>
       </c>
       <c r="O14" t="n">
-        <v>7.0573</v>
+        <v>7.1816</v>
       </c>
     </row>
     <row r="15">
@@ -8848,40 +8848,40 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5.2244</v>
+        <v>5.3159</v>
       </c>
       <c r="E17" t="n">
-        <v>3.9855</v>
+        <v>4.0768</v>
       </c>
       <c r="F17" t="n">
-        <v>4.2205</v>
+        <v>4.3118</v>
       </c>
       <c r="G17" t="n">
-        <v>4.2205</v>
+        <v>4.3118</v>
       </c>
       <c r="H17" t="n">
-        <v>6.2292</v>
+        <v>6.3207</v>
       </c>
       <c r="I17" t="n">
-        <v>5.2144</v>
+        <v>5.3058</v>
       </c>
       <c r="J17" t="n">
-        <v>5.2345</v>
+        <v>5.3259</v>
       </c>
       <c r="K17" t="n">
-        <v>2.7162</v>
+        <v>2.8074</v>
       </c>
       <c r="L17" t="n">
-        <v>7.7379</v>
+        <v>7.8296</v>
       </c>
       <c r="M17" t="n">
-        <v>5.3223</v>
+        <v>5.4137</v>
       </c>
       <c r="N17" t="n">
-        <v>5.1266</v>
+        <v>5.218</v>
       </c>
       <c r="O17" t="n">
-        <v>6.6825</v>
+        <v>6.774</v>
       </c>
     </row>
     <row r="18">
@@ -9001,40 +9001,40 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5.2314</v>
+        <v>5.2862</v>
       </c>
       <c r="E20" t="n">
-        <v>4.1004</v>
+        <v>4.1551</v>
       </c>
       <c r="F20" t="n">
-        <v>4.2275</v>
+        <v>4.2822</v>
       </c>
       <c r="G20" t="n">
-        <v>4.2275</v>
+        <v>4.2822</v>
       </c>
       <c r="H20" t="n">
-        <v>6.2362</v>
+        <v>6.291</v>
       </c>
       <c r="I20" t="n">
-        <v>5.2214</v>
+        <v>5.2761</v>
       </c>
       <c r="J20" t="n">
-        <v>5.2415</v>
+        <v>5.2962</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7231</v>
+        <v>2.7778</v>
       </c>
       <c r="L20" t="n">
-        <v>7.745</v>
+        <v>7.7998</v>
       </c>
       <c r="M20" t="n">
-        <v>5.2329</v>
+        <v>5.2877</v>
       </c>
       <c r="N20" t="n">
-        <v>5.2299</v>
+        <v>5.2847</v>
       </c>
       <c r="O20" t="n">
-        <v>6.5896</v>
+        <v>6.6444</v>
       </c>
     </row>
     <row r="21">
@@ -9154,40 +9154,40 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5.2266</v>
+        <v>5.2459</v>
       </c>
       <c r="E23" t="n">
-        <v>4.0972</v>
+        <v>4.1165</v>
       </c>
       <c r="F23" t="n">
-        <v>4.2226</v>
+        <v>4.242</v>
       </c>
       <c r="G23" t="n">
-        <v>4.2226</v>
+        <v>4.242</v>
       </c>
       <c r="H23" t="n">
-        <v>6.2314</v>
+        <v>6.2507</v>
       </c>
       <c r="I23" t="n">
-        <v>5.2165</v>
+        <v>5.2359</v>
       </c>
       <c r="J23" t="n">
-        <v>5.2366</v>
+        <v>5.2559</v>
       </c>
       <c r="K23" t="n">
-        <v>2.7183</v>
+        <v>2.7376</v>
       </c>
       <c r="L23" t="n">
-        <v>7.7401</v>
+        <v>7.7595</v>
       </c>
       <c r="M23" t="n">
-        <v>5.2266</v>
+        <v>5.2459</v>
       </c>
       <c r="N23" t="n">
-        <v>5.2266</v>
+        <v>5.2459</v>
       </c>
       <c r="O23" t="n">
-        <v>6.5832</v>
+        <v>6.6026</v>
       </c>
     </row>
     <row r="24">

--- a/optimize_prep/output/curves_inspection.xlsx
+++ b/optimize_prep/output/curves_inspection.xlsx
@@ -1463,76 +1463,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.94685</v>
+        <v>0.946865</v>
       </c>
       <c r="D13" t="n">
-        <v>5.2071</v>
+        <v>5.1879</v>
       </c>
       <c r="E13" t="n">
-        <v>0.943835</v>
+        <v>0.94385</v>
       </c>
       <c r="F13" t="n">
-        <v>4.1416</v>
+        <v>4.1224</v>
       </c>
       <c r="G13" t="n">
-        <v>0.956366</v>
+        <v>0.956381</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2032</v>
+        <v>4.184</v>
       </c>
       <c r="I13" t="n">
-        <v>0.956366</v>
+        <v>0.956381</v>
       </c>
       <c r="J13" t="n">
-        <v>4.2032</v>
+        <v>4.184</v>
       </c>
       <c r="K13" t="n">
-        <v>0.937428</v>
+        <v>0.937443</v>
       </c>
       <c r="L13" t="n">
-        <v>6.2119</v>
+        <v>6.1927</v>
       </c>
       <c r="M13" t="n">
-        <v>0.946944</v>
+        <v>0.94696</v>
       </c>
       <c r="N13" t="n">
-        <v>5.1971</v>
+        <v>5.1779</v>
       </c>
       <c r="O13" t="n">
-        <v>0.946755</v>
+        <v>0.94677</v>
       </c>
       <c r="P13" t="n">
-        <v>5.2172</v>
+        <v>5.198</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.970819</v>
+        <v>0.970835</v>
       </c>
       <c r="R13" t="n">
-        <v>2.6989</v>
+        <v>2.6797</v>
       </c>
       <c r="S13" t="n">
-        <v>0.923472</v>
+        <v>0.9234869999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>7.7206</v>
+        <v>7.7014</v>
       </c>
       <c r="U13" t="n">
-        <v>0.95912</v>
+        <v>0.959135</v>
       </c>
       <c r="V13" t="n">
-        <v>5.1502</v>
+        <v>5.131</v>
       </c>
       <c r="W13" t="n">
-        <v>0.934737</v>
+        <v>0.934752</v>
       </c>
       <c r="X13" t="n">
-        <v>5.2641</v>
+        <v>5.2449</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.946694</v>
+        <v>0.946709</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.5047</v>
+        <v>6.4855</v>
       </c>
     </row>
     <row r="14">
@@ -1545,76 +1545,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.923237</v>
+        <v>0.925861</v>
       </c>
       <c r="D14" t="n">
-        <v>5.3342</v>
+        <v>5.1576</v>
       </c>
       <c r="E14" t="n">
-        <v>0.926696</v>
+        <v>0.929329</v>
       </c>
       <c r="F14" t="n">
-        <v>3.7845</v>
+        <v>3.6082</v>
       </c>
       <c r="G14" t="n">
-        <v>0.93719</v>
+        <v>0.939854</v>
       </c>
       <c r="H14" t="n">
-        <v>4.3301</v>
+        <v>4.1537</v>
       </c>
       <c r="I14" t="n">
-        <v>0.93719</v>
+        <v>0.939854</v>
       </c>
       <c r="J14" t="n">
-        <v>4.3301</v>
+        <v>4.1537</v>
       </c>
       <c r="K14" t="n">
-        <v>0.909492</v>
+        <v>0.912077</v>
       </c>
       <c r="L14" t="n">
-        <v>6.339</v>
+        <v>6.1623</v>
       </c>
       <c r="M14" t="n">
-        <v>0.923376</v>
+        <v>0.926</v>
       </c>
       <c r="N14" t="n">
-        <v>5.3241</v>
+        <v>5.1475</v>
       </c>
       <c r="O14" t="n">
-        <v>0.923099</v>
+        <v>0.925722</v>
       </c>
       <c r="P14" t="n">
-        <v>5.3442</v>
+        <v>5.1676</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.958516</v>
+        <v>0.96124</v>
       </c>
       <c r="R14" t="n">
-        <v>2.8257</v>
+        <v>2.6494</v>
       </c>
       <c r="S14" t="n">
-        <v>0.889257</v>
+        <v>0.891784</v>
       </c>
       <c r="T14" t="n">
-        <v>7.8479</v>
+        <v>7.6709</v>
       </c>
       <c r="U14" t="n">
-        <v>0.934115</v>
+        <v>0.93677</v>
       </c>
       <c r="V14" t="n">
-        <v>5.7093</v>
+        <v>5.5327</v>
       </c>
       <c r="W14" t="n">
-        <v>0.912486</v>
+        <v>0.915079</v>
       </c>
       <c r="X14" t="n">
-        <v>4.9591</v>
+        <v>4.7826</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.9157729999999999</v>
+        <v>0.9183750000000001</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.0799</v>
+        <v>6.9031</v>
       </c>
     </row>
     <row r="15">
@@ -1627,76 +1627,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.898998</v>
+        <v>0.902322</v>
       </c>
       <c r="D15" t="n">
-        <v>5.3321</v>
+        <v>5.1643</v>
       </c>
       <c r="E15" t="n">
-        <v>0.909738</v>
+        <v>0.913102</v>
       </c>
       <c r="F15" t="n">
-        <v>3.6704</v>
+        <v>3.5028</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9171589999999999</v>
+        <v>0.920551</v>
       </c>
       <c r="H15" t="n">
-        <v>4.3281</v>
+        <v>4.1604</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9171589999999999</v>
+        <v>0.920551</v>
       </c>
       <c r="J15" t="n">
-        <v>4.3281</v>
+        <v>4.1604</v>
       </c>
       <c r="K15" t="n">
-        <v>0.881196</v>
+        <v>0.884455</v>
       </c>
       <c r="L15" t="n">
-        <v>6.337</v>
+        <v>6.169</v>
       </c>
       <c r="M15" t="n">
-        <v>0.899178</v>
+        <v>0.9025030000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>5.3221</v>
+        <v>5.1542</v>
       </c>
       <c r="O15" t="n">
-        <v>0.898818</v>
+        <v>0.902142</v>
       </c>
       <c r="P15" t="n">
-        <v>5.3421</v>
+        <v>5.1743</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.94509</v>
+        <v>0.948585</v>
       </c>
       <c r="R15" t="n">
-        <v>2.8236</v>
+        <v>2.6561</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8551530000000001</v>
+        <v>0.858316</v>
       </c>
       <c r="T15" t="n">
-        <v>7.8458</v>
+        <v>7.6776</v>
       </c>
       <c r="U15" t="n">
-        <v>0.907555</v>
+        <v>0.910911</v>
       </c>
       <c r="V15" t="n">
-        <v>5.8073</v>
+        <v>5.6394</v>
       </c>
       <c r="W15" t="n">
-        <v>0.890521</v>
+        <v>0.893815</v>
       </c>
       <c r="X15" t="n">
-        <v>4.857</v>
+        <v>4.6892</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.883678</v>
+        <v>0.886946</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.1816</v>
+        <v>7.0135</v>
       </c>
     </row>
     <row r="16">
@@ -1709,76 +1709,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.875404</v>
+        <v>0.879355</v>
       </c>
       <c r="D16" t="n">
-        <v>5.3298</v>
+        <v>5.1703</v>
       </c>
       <c r="E16" t="n">
-        <v>0.893151</v>
+        <v>0.897182</v>
       </c>
       <c r="F16" t="n">
-        <v>3.7091</v>
+        <v>3.5498</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8975649999999999</v>
+        <v>0.901616</v>
       </c>
       <c r="H16" t="n">
-        <v>4.3258</v>
+        <v>4.1664</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8975649999999999</v>
+        <v>0.901616</v>
       </c>
       <c r="J16" t="n">
-        <v>4.3258</v>
+        <v>4.1664</v>
       </c>
       <c r="K16" t="n">
-        <v>0.85379</v>
+        <v>0.857643</v>
       </c>
       <c r="L16" t="n">
-        <v>6.3346</v>
+        <v>6.175</v>
       </c>
       <c r="M16" t="n">
-        <v>0.875623</v>
+        <v>0.879574</v>
       </c>
       <c r="N16" t="n">
-        <v>5.3197</v>
+        <v>5.1602</v>
       </c>
       <c r="O16" t="n">
-        <v>0.875185</v>
+        <v>0.879135</v>
       </c>
       <c r="P16" t="n">
-        <v>5.3398</v>
+        <v>5.1803</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.931863</v>
+        <v>0.936068</v>
       </c>
       <c r="R16" t="n">
-        <v>2.8213</v>
+        <v>2.6621</v>
       </c>
       <c r="S16" t="n">
-        <v>0.822366</v>
+        <v>0.826077</v>
       </c>
       <c r="T16" t="n">
-        <v>7.8435</v>
+        <v>7.6837</v>
       </c>
       <c r="U16" t="n">
-        <v>0.881715</v>
+        <v>0.885694</v>
       </c>
       <c r="V16" t="n">
-        <v>5.7684</v>
+        <v>5.6089</v>
       </c>
       <c r="W16" t="n">
-        <v>0.869139</v>
+        <v>0.873061</v>
       </c>
       <c r="X16" t="n">
-        <v>4.8913</v>
+        <v>4.7319</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.852672</v>
+        <v>0.8565199999999999</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.1413</v>
+        <v>6.9816</v>
       </c>
     </row>
     <row r="17">
@@ -1791,76 +1791,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.85244</v>
+        <v>0.856947</v>
       </c>
       <c r="D17" t="n">
-        <v>5.3273</v>
+        <v>5.1757</v>
       </c>
       <c r="E17" t="n">
-        <v>0.876547</v>
+        <v>0.881182</v>
       </c>
       <c r="F17" t="n">
-        <v>3.7974</v>
+        <v>3.646</v>
       </c>
       <c r="G17" t="n">
-        <v>0.878401</v>
+        <v>0.883045</v>
       </c>
       <c r="H17" t="n">
-        <v>4.3232</v>
+        <v>4.1718</v>
       </c>
       <c r="I17" t="n">
-        <v>0.878401</v>
+        <v>0.883045</v>
       </c>
       <c r="J17" t="n">
-        <v>4.3232</v>
+        <v>4.1718</v>
       </c>
       <c r="K17" t="n">
-        <v>0.827247</v>
+        <v>0.8316210000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>6.3321</v>
+        <v>6.1804</v>
       </c>
       <c r="M17" t="n">
-        <v>0.852696</v>
+        <v>0.857205</v>
       </c>
       <c r="N17" t="n">
-        <v>5.3172</v>
+        <v>5.1656</v>
       </c>
       <c r="O17" t="n">
-        <v>0.852185</v>
+        <v>0.85669</v>
       </c>
       <c r="P17" t="n">
-        <v>5.3373</v>
+        <v>5.1857</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.918832</v>
+        <v>0.92369</v>
       </c>
       <c r="R17" t="n">
-        <v>2.8188</v>
+        <v>2.6675</v>
       </c>
       <c r="S17" t="n">
-        <v>0.790846</v>
+        <v>0.795027</v>
       </c>
       <c r="T17" t="n">
-        <v>7.841</v>
+        <v>7.6891</v>
       </c>
       <c r="U17" t="n">
-        <v>0.856908</v>
+        <v>0.861439</v>
       </c>
       <c r="V17" t="n">
-        <v>5.6848</v>
+        <v>5.5332</v>
       </c>
       <c r="W17" t="n">
-        <v>0.847996</v>
+        <v>0.852479</v>
       </c>
       <c r="X17" t="n">
-        <v>4.9698</v>
+        <v>4.8183</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.823051</v>
+        <v>0.827402</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.0547</v>
+        <v>6.9029</v>
       </c>
     </row>
     <row r="18">
@@ -1873,76 +1873,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.83009</v>
+        <v>0.83509</v>
       </c>
       <c r="D18" t="n">
-        <v>5.3246</v>
+        <v>5.1805</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8598519999999999</v>
+        <v>0.865031</v>
       </c>
       <c r="F18" t="n">
-        <v>3.8904</v>
+        <v>3.7465</v>
       </c>
       <c r="G18" t="n">
-        <v>0.859657</v>
+        <v>0.864836</v>
       </c>
       <c r="H18" t="n">
-        <v>4.3205</v>
+        <v>4.1766</v>
       </c>
       <c r="I18" t="n">
-        <v>0.859657</v>
+        <v>0.864836</v>
       </c>
       <c r="J18" t="n">
-        <v>4.3205</v>
+        <v>4.1766</v>
       </c>
       <c r="K18" t="n">
-        <v>0.801539</v>
+        <v>0.8063669999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>6.3294</v>
+        <v>6.1853</v>
       </c>
       <c r="M18" t="n">
-        <v>0.83038</v>
+        <v>0.835382</v>
       </c>
       <c r="N18" t="n">
-        <v>5.3145</v>
+        <v>5.1705</v>
       </c>
       <c r="O18" t="n">
-        <v>0.829799</v>
+        <v>0.834798</v>
       </c>
       <c r="P18" t="n">
-        <v>5.3346</v>
+        <v>5.1906</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.905995</v>
+        <v>0.911452</v>
       </c>
       <c r="R18" t="n">
-        <v>2.8161</v>
+        <v>2.6724</v>
       </c>
       <c r="S18" t="n">
-        <v>0.760544</v>
+        <v>0.7651250000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>7.8383</v>
+        <v>7.6939</v>
       </c>
       <c r="U18" t="n">
-        <v>0.833166</v>
+        <v>0.838185</v>
       </c>
       <c r="V18" t="n">
-        <v>5.5966</v>
+        <v>5.4525</v>
       </c>
       <c r="W18" t="n">
-        <v>0.827024</v>
+        <v>0.832006</v>
       </c>
       <c r="X18" t="n">
-        <v>5.0526</v>
+        <v>4.9086</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.79482</v>
+        <v>0.799608</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.9634</v>
+        <v>6.8192</v>
       </c>
     </row>
     <row r="19">
@@ -1955,76 +1955,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.8083360000000001</v>
+        <v>0.8137720000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>5.3217</v>
+        <v>5.1849</v>
       </c>
       <c r="E19" t="n">
-        <v>0.843114</v>
+        <v>0.848783</v>
       </c>
       <c r="F19" t="n">
-        <v>3.9701</v>
+        <v>3.8334</v>
       </c>
       <c r="G19" t="n">
-        <v>0.841325</v>
+        <v>0.846982</v>
       </c>
       <c r="H19" t="n">
-        <v>4.3177</v>
+        <v>4.181</v>
       </c>
       <c r="I19" t="n">
-        <v>0.841325</v>
+        <v>0.846982</v>
       </c>
       <c r="J19" t="n">
-        <v>4.3177</v>
+        <v>4.181</v>
       </c>
       <c r="K19" t="n">
-        <v>0.776641</v>
+        <v>0.781863</v>
       </c>
       <c r="L19" t="n">
-        <v>6.3266</v>
+        <v>6.1896</v>
       </c>
       <c r="M19" t="n">
-        <v>0.808659</v>
+        <v>0.814097</v>
       </c>
       <c r="N19" t="n">
-        <v>5.3117</v>
+        <v>5.1749</v>
       </c>
       <c r="O19" t="n">
-        <v>0.808013</v>
+        <v>0.813446</v>
       </c>
       <c r="P19" t="n">
-        <v>5.3318</v>
+        <v>5.1949</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.8933489999999999</v>
+        <v>0.899357</v>
       </c>
       <c r="R19" t="n">
-        <v>2.8133</v>
+        <v>2.6767</v>
       </c>
       <c r="S19" t="n">
-        <v>0.731413</v>
+        <v>0.736331</v>
       </c>
       <c r="T19" t="n">
-        <v>7.8354</v>
+        <v>7.6983</v>
       </c>
       <c r="U19" t="n">
-        <v>0.810412</v>
+        <v>0.8158609999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>5.5201</v>
+        <v>5.3832</v>
       </c>
       <c r="W19" t="n">
-        <v>0.806266</v>
+        <v>0.811687</v>
       </c>
       <c r="X19" t="n">
-        <v>5.1234</v>
+        <v>4.9866</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.76788</v>
+        <v>0.773044</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.8842</v>
+        <v>6.7472</v>
       </c>
     </row>
     <row r="20">
@@ -2037,76 +2037,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.787164</v>
+        <v>0.792981</v>
       </c>
       <c r="D20" t="n">
-        <v>5.3188</v>
+        <v>5.1888</v>
       </c>
       <c r="E20" t="n">
-        <v>0.826417</v>
+        <v>0.832524</v>
       </c>
       <c r="F20" t="n">
-        <v>4.0316</v>
+        <v>3.9017</v>
       </c>
       <c r="G20" t="n">
-        <v>0.823395</v>
+        <v>0.829481</v>
       </c>
       <c r="H20" t="n">
-        <v>4.3148</v>
+        <v>4.1849</v>
       </c>
       <c r="I20" t="n">
-        <v>0.823395</v>
+        <v>0.829481</v>
       </c>
       <c r="J20" t="n">
-        <v>4.3148</v>
+        <v>4.1849</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7525269999999999</v>
+        <v>0.758088</v>
       </c>
       <c r="L20" t="n">
-        <v>6.3237</v>
+        <v>6.1935</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7875180000000001</v>
+        <v>0.793338</v>
       </c>
       <c r="N20" t="n">
-        <v>5.3088</v>
+        <v>5.1787</v>
       </c>
       <c r="O20" t="n">
-        <v>0.78681</v>
+        <v>0.792625</v>
       </c>
       <c r="P20" t="n">
-        <v>5.3289</v>
+        <v>5.1988</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.880893</v>
+        <v>0.8874030000000001</v>
       </c>
       <c r="R20" t="n">
-        <v>2.8104</v>
+        <v>2.6806</v>
       </c>
       <c r="S20" t="n">
-        <v>0.703407</v>
+        <v>0.708606</v>
       </c>
       <c r="T20" t="n">
-        <v>7.8325</v>
+        <v>7.7022</v>
       </c>
       <c r="U20" t="n">
-        <v>0.788542</v>
+        <v>0.79437</v>
       </c>
       <c r="V20" t="n">
-        <v>5.4596</v>
+        <v>5.3296</v>
       </c>
       <c r="W20" t="n">
-        <v>0.785788</v>
+        <v>0.791595</v>
       </c>
       <c r="X20" t="n">
-        <v>5.178</v>
+        <v>5.048</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.742111</v>
+        <v>0.747595</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.8216</v>
+        <v>6.6914</v>
       </c>
     </row>
     <row r="21">
@@ -2119,76 +2119,76 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.766557</v>
+        <v>0.772708</v>
       </c>
       <c r="D21" t="n">
-        <v>5.3159</v>
+        <v>5.1923</v>
       </c>
       <c r="E21" t="n">
-        <v>0.80984</v>
+        <v>0.816338</v>
       </c>
       <c r="F21" t="n">
-        <v>4.0768</v>
+        <v>3.9534</v>
       </c>
       <c r="G21" t="n">
-        <v>0.80586</v>
+        <v>0.812326</v>
       </c>
       <c r="H21" t="n">
-        <v>4.3118</v>
+        <v>4.1884</v>
       </c>
       <c r="I21" t="n">
-        <v>0.80586</v>
+        <v>0.812326</v>
       </c>
       <c r="J21" t="n">
-        <v>4.3118</v>
+        <v>4.1884</v>
       </c>
       <c r="K21" t="n">
-        <v>0.729172</v>
+        <v>0.735023</v>
       </c>
       <c r="L21" t="n">
-        <v>6.3207</v>
+        <v>6.197</v>
       </c>
       <c r="M21" t="n">
-        <v>0.766941</v>
+        <v>0.773095</v>
       </c>
       <c r="N21" t="n">
-        <v>5.3058</v>
+        <v>5.1822</v>
       </c>
       <c r="O21" t="n">
-        <v>0.766174</v>
+        <v>0.772322</v>
       </c>
       <c r="P21" t="n">
-        <v>5.3259</v>
+        <v>5.2023</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.868623</v>
+        <v>0.875593</v>
       </c>
       <c r="R21" t="n">
-        <v>2.8074</v>
+        <v>2.6841</v>
       </c>
       <c r="S21" t="n">
-        <v>0.676484</v>
+        <v>0.681913</v>
       </c>
       <c r="T21" t="n">
-        <v>7.8296</v>
+        <v>7.7057</v>
       </c>
       <c r="U21" t="n">
-        <v>0.767462</v>
+        <v>0.77362</v>
       </c>
       <c r="V21" t="n">
-        <v>5.4137</v>
+        <v>5.2901</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7656539999999999</v>
+        <v>0.771797</v>
       </c>
       <c r="X21" t="n">
-        <v>5.218</v>
+        <v>5.0945</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.717398</v>
+        <v>0.723154</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.774</v>
+        <v>6.6503</v>
       </c>
     </row>
     <row r="22">
@@ -2201,76 +2201,76 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.726982</v>
+        <v>0.733669</v>
       </c>
       <c r="D22" t="n">
-        <v>5.3098</v>
+        <v>5.1982</v>
       </c>
       <c r="E22" t="n">
-        <v>0.777293</v>
+        <v>0.784443</v>
       </c>
       <c r="F22" t="n">
-        <v>4.1298</v>
+        <v>4.0184</v>
       </c>
       <c r="G22" t="n">
-        <v>0.771936</v>
+        <v>0.779036</v>
       </c>
       <c r="H22" t="n">
-        <v>4.3058</v>
+        <v>4.1943</v>
       </c>
       <c r="I22" t="n">
-        <v>0.771936</v>
+        <v>0.779036</v>
       </c>
       <c r="J22" t="n">
-        <v>4.3058</v>
+        <v>4.1943</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6846449999999999</v>
+        <v>0.690943</v>
       </c>
       <c r="L22" t="n">
-        <v>6.3146</v>
+        <v>6.203</v>
       </c>
       <c r="M22" t="n">
-        <v>0.727418</v>
+        <v>0.734109</v>
       </c>
       <c r="N22" t="n">
-        <v>5.2997</v>
+        <v>5.1882</v>
       </c>
       <c r="O22" t="n">
-        <v>0.726545</v>
+        <v>0.733229</v>
       </c>
       <c r="P22" t="n">
-        <v>5.3198</v>
+        <v>5.2083</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.844632</v>
+        <v>0.852401</v>
       </c>
       <c r="R22" t="n">
-        <v>2.8013</v>
+        <v>2.69</v>
       </c>
       <c r="S22" t="n">
-        <v>0.625719</v>
+        <v>0.631474</v>
       </c>
       <c r="T22" t="n">
-        <v>7.8235</v>
+        <v>7.7117</v>
       </c>
       <c r="U22" t="n">
-        <v>0.72736</v>
+        <v>0.734051</v>
       </c>
       <c r="V22" t="n">
-        <v>5.3549</v>
+        <v>5.2433</v>
       </c>
       <c r="W22" t="n">
-        <v>0.726603</v>
+        <v>0.733287</v>
       </c>
       <c r="X22" t="n">
-        <v>5.2647</v>
+        <v>5.1531</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.670779</v>
+        <v>0.676949</v>
       </c>
       <c r="Z22" t="n">
-        <v>6.7133</v>
+        <v>6.6016</v>
       </c>
     </row>
     <row r="23">
@@ -2283,76 +2283,76 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.689491</v>
+        <v>0.696565</v>
       </c>
       <c r="D23" t="n">
-        <v>5.3037</v>
+        <v>5.203</v>
       </c>
       <c r="E23" t="n">
-        <v>0.745797</v>
+        <v>0.753448</v>
       </c>
       <c r="F23" t="n">
-        <v>4.1519</v>
+        <v>4.0513</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7394849999999999</v>
+        <v>0.747072</v>
       </c>
       <c r="H23" t="n">
-        <v>4.2997</v>
+        <v>4.1991</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7394849999999999</v>
+        <v>0.747072</v>
       </c>
       <c r="J23" t="n">
-        <v>4.2997</v>
+        <v>4.1991</v>
       </c>
       <c r="K23" t="n">
-        <v>0.642877</v>
+        <v>0.649473</v>
       </c>
       <c r="L23" t="n">
-        <v>6.3085</v>
+        <v>6.2077</v>
       </c>
       <c r="M23" t="n">
-        <v>0.689974</v>
+        <v>0.697053</v>
       </c>
       <c r="N23" t="n">
-        <v>5.2936</v>
+        <v>5.1929</v>
       </c>
       <c r="O23" t="n">
-        <v>0.689008</v>
+        <v>0.6960769999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>5.3137</v>
+        <v>5.213</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.821353</v>
+        <v>0.82978</v>
       </c>
       <c r="R23" t="n">
-        <v>2.7952</v>
+        <v>2.6948</v>
       </c>
       <c r="S23" t="n">
-        <v>0.578798</v>
+        <v>0.584736</v>
       </c>
       <c r="T23" t="n">
-        <v>7.8173</v>
+        <v>7.7164</v>
       </c>
       <c r="U23" t="n">
-        <v>0.689645</v>
+        <v>0.696721</v>
       </c>
       <c r="V23" t="n">
-        <v>5.3236</v>
+        <v>5.2229</v>
       </c>
       <c r="W23" t="n">
-        <v>0.689337</v>
+        <v>0.6964089999999999</v>
       </c>
       <c r="X23" t="n">
-        <v>5.2838</v>
+        <v>5.1831</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.627463</v>
+        <v>0.633901</v>
       </c>
       <c r="Z23" t="n">
-        <v>6.681</v>
+        <v>6.5802</v>
       </c>
     </row>
     <row r="24">
@@ -2365,76 +2365,76 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.653973</v>
+        <v>0.66131</v>
       </c>
       <c r="D24" t="n">
-        <v>5.2977</v>
+        <v>5.2068</v>
       </c>
       <c r="E24" t="n">
-        <v>0.715485</v>
+        <v>0.723512</v>
       </c>
       <c r="F24" t="n">
-        <v>4.1586</v>
+        <v>4.0678</v>
       </c>
       <c r="G24" t="n">
-        <v>0.708441</v>
+        <v>0.716388</v>
       </c>
       <c r="H24" t="n">
-        <v>4.2937</v>
+        <v>4.2028</v>
       </c>
       <c r="I24" t="n">
-        <v>0.708441</v>
+        <v>0.716388</v>
       </c>
       <c r="J24" t="n">
-        <v>4.2937</v>
+        <v>4.2028</v>
       </c>
       <c r="K24" t="n">
-        <v>0.603693</v>
+        <v>0.610466</v>
       </c>
       <c r="L24" t="n">
-        <v>6.3025</v>
+        <v>6.2115</v>
       </c>
       <c r="M24" t="n">
-        <v>0.654496</v>
+        <v>0.661839</v>
       </c>
       <c r="N24" t="n">
-        <v>5.2876</v>
+        <v>5.1967</v>
       </c>
       <c r="O24" t="n">
-        <v>0.65345</v>
+        <v>0.660781</v>
       </c>
       <c r="P24" t="n">
-        <v>5.3077</v>
+        <v>5.2168</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.798764</v>
+        <v>0.8077260000000001</v>
       </c>
       <c r="R24" t="n">
-        <v>2.7892</v>
+        <v>2.6985</v>
       </c>
       <c r="S24" t="n">
-        <v>0.535428</v>
+        <v>0.541435</v>
       </c>
       <c r="T24" t="n">
-        <v>7.8113</v>
+        <v>7.7202</v>
       </c>
       <c r="U24" t="n">
-        <v>0.654034</v>
+        <v>0.661372</v>
       </c>
       <c r="V24" t="n">
-        <v>5.3062</v>
+        <v>5.2153</v>
       </c>
       <c r="W24" t="n">
-        <v>0.653912</v>
+        <v>0.6612479999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>5.2891</v>
+        <v>5.1982</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.587081</v>
+        <v>0.593668</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.6632</v>
+        <v>6.5723</v>
       </c>
     </row>
     <row r="25">
@@ -2447,76 +2447,76 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.620322</v>
+        <v>0.627818</v>
       </c>
       <c r="D25" t="n">
-        <v>5.2918</v>
+        <v>5.2098</v>
       </c>
       <c r="E25" t="n">
-        <v>0.686389</v>
+        <v>0.694684</v>
       </c>
       <c r="F25" t="n">
-        <v>4.1583</v>
+        <v>4.0764</v>
       </c>
       <c r="G25" t="n">
-        <v>0.67874</v>
+        <v>0.686943</v>
       </c>
       <c r="H25" t="n">
-        <v>4.2878</v>
+        <v>4.2059</v>
       </c>
       <c r="I25" t="n">
-        <v>0.67874</v>
+        <v>0.686943</v>
       </c>
       <c r="J25" t="n">
-        <v>4.2878</v>
+        <v>4.2059</v>
       </c>
       <c r="K25" t="n">
-        <v>0.566931</v>
+        <v>0.573783</v>
       </c>
       <c r="L25" t="n">
-        <v>6.2966</v>
+        <v>6.2145</v>
       </c>
       <c r="M25" t="n">
-        <v>0.62088</v>
+        <v>0.6283840000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>5.2817</v>
+        <v>5.1997</v>
       </c>
       <c r="O25" t="n">
-        <v>0.619763</v>
+        <v>0.6272529999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>5.3018</v>
+        <v>5.2198</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.776843</v>
+        <v>0.786231</v>
       </c>
       <c r="R25" t="n">
-        <v>2.7834</v>
+        <v>2.7016</v>
       </c>
       <c r="S25" t="n">
-        <v>0.495337</v>
+        <v>0.501323</v>
       </c>
       <c r="T25" t="n">
-        <v>7.8054</v>
+        <v>7.7233</v>
       </c>
       <c r="U25" t="n">
-        <v>0.620346</v>
+        <v>0.627843</v>
       </c>
       <c r="V25" t="n">
-        <v>5.2954</v>
+        <v>5.2134</v>
       </c>
       <c r="W25" t="n">
-        <v>0.620297</v>
+        <v>0.627794</v>
       </c>
       <c r="X25" t="n">
-        <v>5.2882</v>
+        <v>5.2062</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.549373</v>
+        <v>0.556013</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.6522</v>
+        <v>6.5701</v>
       </c>
     </row>
     <row r="26">
@@ -2529,76 +2529,76 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.588435</v>
+        <v>0.596007</v>
       </c>
       <c r="D26" t="n">
-        <v>5.2862</v>
+        <v>5.2122</v>
       </c>
       <c r="E26" t="n">
-        <v>0.65849</v>
+        <v>0.666963</v>
       </c>
       <c r="F26" t="n">
-        <v>4.1551</v>
+        <v>4.0811</v>
       </c>
       <c r="G26" t="n">
-        <v>0.650321</v>
+        <v>0.658689</v>
       </c>
       <c r="H26" t="n">
-        <v>4.2822</v>
+        <v>4.2082</v>
       </c>
       <c r="I26" t="n">
-        <v>0.650321</v>
+        <v>0.658689</v>
       </c>
       <c r="J26" t="n">
-        <v>4.2822</v>
+        <v>4.2082</v>
       </c>
       <c r="K26" t="n">
-        <v>0.532438</v>
+        <v>0.539289</v>
       </c>
       <c r="L26" t="n">
-        <v>6.291</v>
+        <v>6.2169</v>
       </c>
       <c r="M26" t="n">
-        <v>0.589024</v>
+        <v>0.596603</v>
       </c>
       <c r="N26" t="n">
-        <v>5.2761</v>
+        <v>5.2021</v>
       </c>
       <c r="O26" t="n">
-        <v>0.587847</v>
+        <v>0.595411</v>
       </c>
       <c r="P26" t="n">
-        <v>5.2962</v>
+        <v>5.2222</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.755566</v>
+        <v>0.765288</v>
       </c>
       <c r="R26" t="n">
-        <v>2.7778</v>
+        <v>2.7039</v>
       </c>
       <c r="S26" t="n">
-        <v>0.458274</v>
+        <v>0.464171</v>
       </c>
       <c r="T26" t="n">
-        <v>7.7998</v>
+        <v>7.7257</v>
       </c>
       <c r="U26" t="n">
-        <v>0.588445</v>
+        <v>0.596016</v>
       </c>
       <c r="V26" t="n">
-        <v>5.2877</v>
+        <v>5.2137</v>
       </c>
       <c r="W26" t="n">
-        <v>0.588426</v>
+        <v>0.595997</v>
       </c>
       <c r="X26" t="n">
-        <v>5.2847</v>
+        <v>5.2107</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.514134</v>
+        <v>0.520749</v>
       </c>
       <c r="Z26" t="n">
-        <v>6.6444</v>
+        <v>6.5703</v>
       </c>
     </row>
     <row r="27">
@@ -2611,76 +2611,76 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.452312</v>
+        <v>0.459447</v>
       </c>
       <c r="D27" t="n">
-        <v>5.2624</v>
+        <v>5.2183</v>
       </c>
       <c r="E27" t="n">
-        <v>0.535458</v>
+        <v>0.5439040000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>4.133</v>
+        <v>4.0889</v>
       </c>
       <c r="G27" t="n">
-        <v>0.525512</v>
+        <v>0.533801</v>
       </c>
       <c r="H27" t="n">
-        <v>4.2584</v>
+        <v>4.2143</v>
       </c>
       <c r="I27" t="n">
-        <v>0.525512</v>
+        <v>0.533801</v>
       </c>
       <c r="J27" t="n">
-        <v>4.2584</v>
+        <v>4.2143</v>
       </c>
       <c r="K27" t="n">
-        <v>0.389309</v>
+        <v>0.395449</v>
       </c>
       <c r="L27" t="n">
-        <v>6.2672</v>
+        <v>6.223</v>
       </c>
       <c r="M27" t="n">
-        <v>0.452991</v>
+        <v>0.460136</v>
       </c>
       <c r="N27" t="n">
-        <v>5.2523</v>
+        <v>5.2082</v>
       </c>
       <c r="O27" t="n">
-        <v>0.451634</v>
+        <v>0.458758</v>
       </c>
       <c r="P27" t="n">
-        <v>5.2724</v>
+        <v>5.2283</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.65811</v>
+        <v>0.6684909999999999</v>
       </c>
       <c r="R27" t="n">
-        <v>2.754</v>
+        <v>2.71</v>
       </c>
       <c r="S27" t="n">
-        <v>0.310869</v>
+        <v>0.315773</v>
       </c>
       <c r="T27" t="n">
-        <v>7.776</v>
+        <v>7.7317</v>
       </c>
       <c r="U27" t="n">
-        <v>0.452312</v>
+        <v>0.459447</v>
       </c>
       <c r="V27" t="n">
-        <v>5.2624</v>
+        <v>5.2183</v>
       </c>
       <c r="W27" t="n">
-        <v>0.452312</v>
+        <v>0.459447</v>
       </c>
       <c r="X27" t="n">
-        <v>5.2624</v>
+        <v>5.2183</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.369397</v>
+        <v>0.375224</v>
       </c>
       <c r="Z27" t="n">
-        <v>6.6191</v>
+        <v>6.5749</v>
       </c>
     </row>
     <row r="28">
@@ -2693,76 +2693,76 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.348024</v>
+        <v>0.354117</v>
       </c>
       <c r="D28" t="n">
-        <v>5.2459</v>
+        <v>5.2198</v>
       </c>
       <c r="E28" t="n">
-        <v>0.435839</v>
+        <v>0.443469</v>
       </c>
       <c r="F28" t="n">
-        <v>4.1165</v>
+        <v>4.0904</v>
       </c>
       <c r="G28" t="n">
-        <v>0.425078</v>
+        <v>0.43252</v>
       </c>
       <c r="H28" t="n">
-        <v>4.242</v>
+        <v>4.2158</v>
       </c>
       <c r="I28" t="n">
-        <v>0.425078</v>
+        <v>0.43252</v>
       </c>
       <c r="J28" t="n">
-        <v>4.242</v>
+        <v>4.2158</v>
       </c>
       <c r="K28" t="n">
-        <v>0.284938</v>
+        <v>0.289926</v>
       </c>
       <c r="L28" t="n">
-        <v>6.2507</v>
+        <v>6.2245</v>
       </c>
       <c r="M28" t="n">
-        <v>0.348721</v>
+        <v>0.354826</v>
       </c>
       <c r="N28" t="n">
-        <v>5.2359</v>
+        <v>5.2097</v>
       </c>
       <c r="O28" t="n">
-        <v>0.347329</v>
+        <v>0.353409</v>
       </c>
       <c r="P28" t="n">
-        <v>5.2559</v>
+        <v>5.2298</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.5737950000000001</v>
+        <v>0.58384</v>
       </c>
       <c r="R28" t="n">
-        <v>2.7376</v>
+        <v>2.7115</v>
       </c>
       <c r="S28" t="n">
-        <v>0.211087</v>
+        <v>0.214783</v>
       </c>
       <c r="T28" t="n">
-        <v>7.7595</v>
+        <v>7.7332</v>
       </c>
       <c r="U28" t="n">
-        <v>0.348024</v>
+        <v>0.354117</v>
       </c>
       <c r="V28" t="n">
-        <v>5.2459</v>
+        <v>5.2198</v>
       </c>
       <c r="W28" t="n">
-        <v>0.348024</v>
+        <v>0.354117</v>
       </c>
       <c r="X28" t="n">
-        <v>5.2459</v>
+        <v>5.2198</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.265675</v>
+        <v>0.270326</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.6026</v>
+        <v>6.5764</v>
       </c>
     </row>
     <row r="29">
@@ -2775,76 +2775,76 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.26796</v>
+        <v>0.272926</v>
       </c>
       <c r="D29" t="n">
-        <v>5.2352</v>
+        <v>5.2199</v>
       </c>
       <c r="E29" t="n">
-        <v>0.35499</v>
+        <v>0.361568</v>
       </c>
       <c r="F29" t="n">
-        <v>4.1059</v>
+        <v>4.0905</v>
       </c>
       <c r="G29" t="n">
-        <v>0.344068</v>
+        <v>0.350444</v>
       </c>
       <c r="H29" t="n">
-        <v>4.2313</v>
+        <v>4.2159</v>
       </c>
       <c r="I29" t="n">
-        <v>0.344068</v>
+        <v>0.350444</v>
       </c>
       <c r="J29" t="n">
-        <v>4.2313</v>
+        <v>4.2159</v>
       </c>
       <c r="K29" t="n">
-        <v>0.208688</v>
+        <v>0.212555</v>
       </c>
       <c r="L29" t="n">
-        <v>6.24</v>
+        <v>6.2247</v>
       </c>
       <c r="M29" t="n">
-        <v>0.268631</v>
+        <v>0.273609</v>
       </c>
       <c r="N29" t="n">
-        <v>5.2252</v>
+        <v>5.2099</v>
       </c>
       <c r="O29" t="n">
-        <v>0.267291</v>
+        <v>0.272244</v>
       </c>
       <c r="P29" t="n">
-        <v>5.2453</v>
+        <v>5.2299</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.5006159999999999</v>
+        <v>0.509892</v>
       </c>
       <c r="R29" t="n">
-        <v>2.727</v>
+        <v>2.7116</v>
       </c>
       <c r="S29" t="n">
-        <v>0.143429</v>
+        <v>0.146087</v>
       </c>
       <c r="T29" t="n">
-        <v>7.7487</v>
+        <v>7.7334</v>
       </c>
       <c r="U29" t="n">
-        <v>0.26796</v>
+        <v>0.272926</v>
       </c>
       <c r="V29" t="n">
-        <v>5.2352</v>
+        <v>5.2199</v>
       </c>
       <c r="W29" t="n">
-        <v>0.26796</v>
+        <v>0.272926</v>
       </c>
       <c r="X29" t="n">
-        <v>5.2352</v>
+        <v>5.2199</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.191204</v>
+        <v>0.194747</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.5919</v>
+        <v>6.5765</v>
       </c>
     </row>
     <row r="30">
@@ -2857,76 +2857,76 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.206417</v>
+        <v>0.210366</v>
       </c>
       <c r="D30" t="n">
-        <v>5.1425</v>
+        <v>5.1337</v>
       </c>
       <c r="E30" t="n">
-        <v>0.289277</v>
+        <v>0.294811</v>
       </c>
       <c r="F30" t="n">
-        <v>4.0317</v>
+        <v>4.023</v>
       </c>
       <c r="G30" t="n">
-        <v>0.27863</v>
+        <v>0.283961</v>
       </c>
       <c r="H30" t="n">
-        <v>4.1551</v>
+        <v>4.1463</v>
       </c>
       <c r="I30" t="n">
-        <v>0.27863</v>
+        <v>0.283961</v>
       </c>
       <c r="J30" t="n">
-        <v>4.1551</v>
+        <v>4.1463</v>
       </c>
       <c r="K30" t="n">
-        <v>0.15292</v>
+        <v>0.155845</v>
       </c>
       <c r="L30" t="n">
-        <v>6.1307</v>
+        <v>6.1219</v>
       </c>
       <c r="M30" t="n">
-        <v>0.207037</v>
+        <v>0.210998</v>
       </c>
       <c r="N30" t="n">
-        <v>5.1326</v>
+        <v>5.1238</v>
       </c>
       <c r="O30" t="n">
-        <v>0.205799</v>
+        <v>0.209736</v>
       </c>
       <c r="P30" t="n">
-        <v>5.1524</v>
+        <v>5.1436</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.43697</v>
+        <v>0.44533</v>
       </c>
       <c r="R30" t="n">
-        <v>2.6756</v>
+        <v>2.6668</v>
       </c>
       <c r="S30" t="n">
-        <v>0.097508</v>
+        <v>0.099373</v>
       </c>
       <c r="T30" t="n">
-        <v>7.6145</v>
+        <v>7.6057</v>
       </c>
       <c r="U30" t="n">
-        <v>0.206417</v>
+        <v>0.210366</v>
       </c>
       <c r="V30" t="n">
-        <v>5.1425</v>
+        <v>5.1337</v>
       </c>
       <c r="W30" t="n">
-        <v>0.206417</v>
+        <v>0.210366</v>
       </c>
       <c r="X30" t="n">
-        <v>5.1425</v>
+        <v>5.1337</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.137678</v>
+        <v>0.140312</v>
       </c>
       <c r="Z30" t="n">
-        <v>6.4767</v>
+        <v>6.4679</v>
       </c>
     </row>
   </sheetData>
@@ -8542,40 +8542,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5.2071</v>
+        <v>5.1879</v>
       </c>
       <c r="E11" t="n">
-        <v>4.1416</v>
+        <v>4.1224</v>
       </c>
       <c r="F11" t="n">
-        <v>4.2032</v>
+        <v>4.184</v>
       </c>
       <c r="G11" t="n">
-        <v>4.2032</v>
+        <v>4.184</v>
       </c>
       <c r="H11" t="n">
-        <v>6.2119</v>
+        <v>6.1927</v>
       </c>
       <c r="I11" t="n">
-        <v>5.1971</v>
+        <v>5.1779</v>
       </c>
       <c r="J11" t="n">
-        <v>5.2172</v>
+        <v>5.198</v>
       </c>
       <c r="K11" t="n">
-        <v>2.6989</v>
+        <v>2.6797</v>
       </c>
       <c r="L11" t="n">
-        <v>7.7206</v>
+        <v>7.7014</v>
       </c>
       <c r="M11" t="n">
-        <v>5.1502</v>
+        <v>5.131</v>
       </c>
       <c r="N11" t="n">
-        <v>5.2641</v>
+        <v>5.2449</v>
       </c>
       <c r="O11" t="n">
-        <v>6.5047</v>
+        <v>6.4855</v>
       </c>
     </row>
     <row r="12">
@@ -8695,40 +8695,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5.3321</v>
+        <v>5.1643</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6704</v>
+        <v>3.5028</v>
       </c>
       <c r="F14" t="n">
-        <v>4.3281</v>
+        <v>4.1604</v>
       </c>
       <c r="G14" t="n">
-        <v>4.3281</v>
+        <v>4.1604</v>
       </c>
       <c r="H14" t="n">
-        <v>6.337</v>
+        <v>6.169</v>
       </c>
       <c r="I14" t="n">
-        <v>5.3221</v>
+        <v>5.1542</v>
       </c>
       <c r="J14" t="n">
-        <v>5.3421</v>
+        <v>5.1743</v>
       </c>
       <c r="K14" t="n">
-        <v>2.8236</v>
+        <v>2.6561</v>
       </c>
       <c r="L14" t="n">
-        <v>7.8458</v>
+        <v>7.6776</v>
       </c>
       <c r="M14" t="n">
-        <v>5.8073</v>
+        <v>5.6394</v>
       </c>
       <c r="N14" t="n">
-        <v>4.857</v>
+        <v>4.6892</v>
       </c>
       <c r="O14" t="n">
-        <v>7.1816</v>
+        <v>7.0135</v>
       </c>
     </row>
     <row r="15">
@@ -8848,40 +8848,40 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5.3159</v>
+        <v>5.1923</v>
       </c>
       <c r="E17" t="n">
-        <v>4.0768</v>
+        <v>3.9534</v>
       </c>
       <c r="F17" t="n">
-        <v>4.3118</v>
+        <v>4.1884</v>
       </c>
       <c r="G17" t="n">
-        <v>4.3118</v>
+        <v>4.1884</v>
       </c>
       <c r="H17" t="n">
-        <v>6.3207</v>
+        <v>6.197</v>
       </c>
       <c r="I17" t="n">
-        <v>5.3058</v>
+        <v>5.1822</v>
       </c>
       <c r="J17" t="n">
-        <v>5.3259</v>
+        <v>5.2023</v>
       </c>
       <c r="K17" t="n">
-        <v>2.8074</v>
+        <v>2.6841</v>
       </c>
       <c r="L17" t="n">
-        <v>7.8296</v>
+        <v>7.7057</v>
       </c>
       <c r="M17" t="n">
-        <v>5.4137</v>
+        <v>5.2901</v>
       </c>
       <c r="N17" t="n">
-        <v>5.218</v>
+        <v>5.0945</v>
       </c>
       <c r="O17" t="n">
-        <v>6.774</v>
+        <v>6.6503</v>
       </c>
     </row>
     <row r="18">
@@ -9001,40 +9001,40 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5.2862</v>
+        <v>5.2122</v>
       </c>
       <c r="E20" t="n">
-        <v>4.1551</v>
+        <v>4.0811</v>
       </c>
       <c r="F20" t="n">
-        <v>4.2822</v>
+        <v>4.2082</v>
       </c>
       <c r="G20" t="n">
-        <v>4.2822</v>
+        <v>4.2082</v>
       </c>
       <c r="H20" t="n">
-        <v>6.291</v>
+        <v>6.2169</v>
       </c>
       <c r="I20" t="n">
-        <v>5.2761</v>
+        <v>5.2021</v>
       </c>
       <c r="J20" t="n">
-        <v>5.2962</v>
+        <v>5.2222</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7778</v>
+        <v>2.7039</v>
       </c>
       <c r="L20" t="n">
-        <v>7.7998</v>
+        <v>7.7257</v>
       </c>
       <c r="M20" t="n">
-        <v>5.2877</v>
+        <v>5.2137</v>
       </c>
       <c r="N20" t="n">
-        <v>5.2847</v>
+        <v>5.2107</v>
       </c>
       <c r="O20" t="n">
-        <v>6.6444</v>
+        <v>6.5703</v>
       </c>
     </row>
     <row r="21">
@@ -9154,40 +9154,40 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5.2459</v>
+        <v>5.2198</v>
       </c>
       <c r="E23" t="n">
-        <v>4.1165</v>
+        <v>4.0904</v>
       </c>
       <c r="F23" t="n">
-        <v>4.242</v>
+        <v>4.2158</v>
       </c>
       <c r="G23" t="n">
-        <v>4.242</v>
+        <v>4.2158</v>
       </c>
       <c r="H23" t="n">
-        <v>6.2507</v>
+        <v>6.2245</v>
       </c>
       <c r="I23" t="n">
-        <v>5.2359</v>
+        <v>5.2097</v>
       </c>
       <c r="J23" t="n">
-        <v>5.2559</v>
+        <v>5.2298</v>
       </c>
       <c r="K23" t="n">
-        <v>2.7376</v>
+        <v>2.7115</v>
       </c>
       <c r="L23" t="n">
-        <v>7.7595</v>
+        <v>7.7332</v>
       </c>
       <c r="M23" t="n">
-        <v>5.2459</v>
+        <v>5.2198</v>
       </c>
       <c r="N23" t="n">
-        <v>5.2459</v>
+        <v>5.2198</v>
       </c>
       <c r="O23" t="n">
-        <v>6.6026</v>
+        <v>6.5764</v>
       </c>
     </row>
     <row r="24">

--- a/optimize_prep/output/curves_inspection.xlsx
+++ b/optimize_prep/output/curves_inspection.xlsx
@@ -561,76 +561,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.995171</v>
+        <v>0.996858</v>
       </c>
       <c r="D2" t="n">
-        <v>5.823</v>
+        <v>3.7828</v>
       </c>
       <c r="E2" t="n">
-        <v>0.993116</v>
+        <v>0.994798</v>
       </c>
       <c r="F2" t="n">
-        <v>8.3186</v>
+        <v>6.2752</v>
       </c>
       <c r="G2" t="n">
-        <v>0.996001</v>
+        <v>0.997689</v>
       </c>
       <c r="H2" t="n">
-        <v>4.8186</v>
+        <v>2.78</v>
       </c>
       <c r="I2" t="n">
-        <v>0.996001</v>
+        <v>0.997689</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8186</v>
+        <v>2.78</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9943419999999999</v>
+        <v>0.996027</v>
       </c>
       <c r="L2" t="n">
-        <v>6.8283</v>
+        <v>4.7863</v>
       </c>
       <c r="M2" t="n">
-        <v>0.995179</v>
+        <v>0.996866</v>
       </c>
       <c r="N2" t="n">
-        <v>5.813</v>
+        <v>3.7727</v>
       </c>
       <c r="O2" t="n">
-        <v>0.995163</v>
+        <v>0.996849</v>
       </c>
       <c r="P2" t="n">
-        <v>5.8331</v>
+        <v>3.7928</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.997246</v>
+        <v>0.998937</v>
       </c>
       <c r="R2" t="n">
-        <v>3.3135</v>
+        <v>1.2775</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9931</v>
+        <v>0.994783</v>
       </c>
       <c r="T2" t="n">
-        <v>8.3378</v>
+        <v>6.2933</v>
       </c>
       <c r="U2" t="n">
-        <v>0.997841</v>
+        <v>0.999533</v>
       </c>
       <c r="V2" t="n">
-        <v>2.5962</v>
+        <v>0.5605</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9925079999999999</v>
+        <v>0.994189</v>
       </c>
       <c r="X2" t="n">
-        <v>9.0585</v>
+        <v>7.0137</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.996815</v>
+        <v>0.998505</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.8347</v>
+        <v>1.7968</v>
       </c>
     </row>
     <row r="3">
@@ -643,76 +643,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.990361</v>
+        <v>0.993656</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8283</v>
+        <v>3.8662</v>
       </c>
       <c r="E3" t="n">
-        <v>0.986752</v>
+        <v>0.990032</v>
       </c>
       <c r="F3" t="n">
-        <v>7.7385</v>
+        <v>5.7768</v>
       </c>
       <c r="G3" t="n">
-        <v>0.992013</v>
+        <v>0.995314</v>
       </c>
       <c r="H3" t="n">
-        <v>4.8238</v>
+        <v>2.8634</v>
       </c>
       <c r="I3" t="n">
-        <v>0.992013</v>
+        <v>0.995314</v>
       </c>
       <c r="J3" t="n">
-        <v>4.8238</v>
+        <v>2.8634</v>
       </c>
       <c r="K3" t="n">
-        <v>0.988712</v>
+        <v>0.992001</v>
       </c>
       <c r="L3" t="n">
-        <v>6.8335</v>
+        <v>4.8699</v>
       </c>
       <c r="M3" t="n">
-        <v>0.990377</v>
+        <v>0.993673</v>
       </c>
       <c r="N3" t="n">
-        <v>5.8182</v>
+        <v>3.8562</v>
       </c>
       <c r="O3" t="n">
-        <v>0.990344</v>
+        <v>0.99364</v>
       </c>
       <c r="P3" t="n">
-        <v>5.8383</v>
+        <v>3.8763</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.994496</v>
+        <v>0.9978050000000001</v>
       </c>
       <c r="R3" t="n">
-        <v>3.3187</v>
+        <v>1.3608</v>
       </c>
       <c r="S3" t="n">
-        <v>0.986243</v>
+        <v>0.989525</v>
       </c>
       <c r="T3" t="n">
-        <v>8.343</v>
+        <v>6.3769</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9952530000000001</v>
+        <v>0.998567</v>
       </c>
       <c r="V3" t="n">
-        <v>3.1212</v>
+        <v>1.1605</v>
       </c>
       <c r="W3" t="n">
-        <v>0.985493</v>
+        <v>0.988769</v>
       </c>
       <c r="X3" t="n">
-        <v>8.541399999999999</v>
+        <v>6.578</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.99319</v>
+        <v>0.996499</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.3788</v>
+        <v>2.416</v>
       </c>
     </row>
     <row r="4">
@@ -725,76 +725,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.985581</v>
+        <v>0.990461</v>
       </c>
       <c r="D4" t="n">
-        <v>5.8198</v>
+        <v>3.8709</v>
       </c>
       <c r="E4" t="n">
-        <v>0.98084</v>
+        <v>0.985693</v>
       </c>
       <c r="F4" t="n">
-        <v>7.2336</v>
+        <v>5.2816</v>
       </c>
       <c r="G4" t="n">
-        <v>0.988048</v>
+        <v>0.99294</v>
       </c>
       <c r="H4" t="n">
-        <v>4.8154</v>
+        <v>2.8681</v>
       </c>
       <c r="I4" t="n">
-        <v>0.988048</v>
+        <v>0.99294</v>
       </c>
       <c r="J4" t="n">
-        <v>4.8154</v>
+        <v>2.8681</v>
       </c>
       <c r="K4" t="n">
-        <v>0.98312</v>
+        <v>0.987988</v>
       </c>
       <c r="L4" t="n">
-        <v>6.8251</v>
+        <v>4.8745</v>
       </c>
       <c r="M4" t="n">
-        <v>0.985606</v>
+        <v>0.990486</v>
       </c>
       <c r="N4" t="n">
-        <v>5.8098</v>
+        <v>3.8609</v>
       </c>
       <c r="O4" t="n">
-        <v>0.985556</v>
+        <v>0.990436</v>
       </c>
       <c r="P4" t="n">
-        <v>5.8299</v>
+        <v>3.8809</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.99176</v>
+        <v>0.996671</v>
       </c>
       <c r="R4" t="n">
-        <v>3.3103</v>
+        <v>1.3654</v>
       </c>
       <c r="S4" t="n">
-        <v>0.97944</v>
+        <v>0.98429</v>
       </c>
       <c r="T4" t="n">
-        <v>8.3346</v>
+        <v>6.3816</v>
       </c>
       <c r="U4" t="n">
-        <v>0.992314</v>
+        <v>0.9972299999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>3.5539</v>
+        <v>1.6094</v>
       </c>
       <c r="W4" t="n">
-        <v>0.978894</v>
+        <v>0.983738</v>
       </c>
       <c r="X4" t="n">
-        <v>8.09</v>
+        <v>6.1367</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.989211</v>
+        <v>0.994112</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.8277</v>
+        <v>2.8812</v>
       </c>
     </row>
     <row r="5">
@@ -807,76 +807,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.980965</v>
+        <v>0.987253</v>
       </c>
       <c r="D5" t="n">
-        <v>5.6462</v>
+        <v>3.8998</v>
       </c>
       <c r="E5" t="n">
-        <v>0.975472</v>
+        <v>0.981717</v>
       </c>
       <c r="F5" t="n">
-        <v>6.6029</v>
+        <v>4.8608</v>
       </c>
       <c r="G5" t="n">
-        <v>0.984241</v>
+        <v>0.990549</v>
       </c>
       <c r="H5" t="n">
-        <v>4.6419</v>
+        <v>2.8969</v>
       </c>
       <c r="I5" t="n">
-        <v>0.984241</v>
+        <v>0.990549</v>
       </c>
       <c r="J5" t="n">
-        <v>4.6419</v>
+        <v>2.8969</v>
       </c>
       <c r="K5" t="n">
-        <v>0.977701</v>
+        <v>0.983967</v>
       </c>
       <c r="L5" t="n">
-        <v>6.6513</v>
+        <v>4.9034</v>
       </c>
       <c r="M5" t="n">
-        <v>0.980998</v>
+        <v>0.987286</v>
       </c>
       <c r="N5" t="n">
-        <v>5.6362</v>
+        <v>3.8897</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9809330000000001</v>
+        <v>0.98722</v>
       </c>
       <c r="P5" t="n">
-        <v>5.6562</v>
+        <v>3.9098</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.989174</v>
+        <v>0.995514</v>
       </c>
       <c r="R5" t="n">
-        <v>3.137</v>
+        <v>1.3942</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9728250000000001</v>
+        <v>0.97906</v>
       </c>
       <c r="T5" t="n">
-        <v>8.160600000000001</v>
+        <v>6.4105</v>
       </c>
       <c r="U5" t="n">
-        <v>0.989192</v>
+        <v>0.995539</v>
       </c>
       <c r="V5" t="n">
-        <v>3.787</v>
+        <v>2.0381</v>
       </c>
       <c r="W5" t="n">
-        <v>0.972807</v>
+        <v>0.979035</v>
       </c>
       <c r="X5" t="n">
-        <v>7.5083</v>
+        <v>5.7643</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.985044</v>
+        <v>0.9913650000000001</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.0756</v>
+        <v>3.3246</v>
       </c>
     </row>
     <row r="6">
@@ -889,76 +889,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.976371</v>
+        <v>0.984054</v>
       </c>
       <c r="D6" t="n">
-        <v>5.6462</v>
+        <v>3.9004</v>
       </c>
       <c r="E6" t="n">
-        <v>0.970444</v>
+        <v>0.9780799999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>6.2181</v>
+        <v>4.4623</v>
       </c>
       <c r="G6" t="n">
-        <v>0.980448</v>
+        <v>0.988163</v>
       </c>
       <c r="H6" t="n">
-        <v>4.6419</v>
+        <v>2.8976</v>
       </c>
       <c r="I6" t="n">
-        <v>0.980448</v>
+        <v>0.988163</v>
       </c>
       <c r="J6" t="n">
-        <v>4.6419</v>
+        <v>2.8976</v>
       </c>
       <c r="K6" t="n">
-        <v>0.972312</v>
+        <v>0.979963</v>
       </c>
       <c r="L6" t="n">
-        <v>6.6513</v>
+        <v>4.9041</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9764119999999999</v>
+        <v>0.9840950000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>5.6361</v>
+        <v>3.8904</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9763309999999999</v>
+        <v>0.984013</v>
       </c>
       <c r="P6" t="n">
-        <v>5.6562</v>
+        <v>3.9104</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.986595</v>
+        <v>0.994358</v>
       </c>
       <c r="R6" t="n">
-        <v>3.137</v>
+        <v>1.3949</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9662539999999999</v>
+        <v>0.973857</v>
       </c>
       <c r="T6" t="n">
-        <v>8.160600000000001</v>
+        <v>6.4111</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9858</v>
+        <v>0.993557</v>
       </c>
       <c r="V6" t="n">
-        <v>4.1294</v>
+        <v>2.3939</v>
       </c>
       <c r="W6" t="n">
-        <v>0.967033</v>
+        <v>0.974642</v>
       </c>
       <c r="X6" t="n">
-        <v>7.1649</v>
+        <v>5.4088</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.980607</v>
+        <v>0.988323</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.4306</v>
+        <v>3.6936</v>
       </c>
     </row>
     <row r="7">
@@ -971,76 +971,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.971817</v>
+        <v>0.980866</v>
       </c>
       <c r="D7" t="n">
-        <v>5.6234</v>
+        <v>3.9004</v>
       </c>
       <c r="E7" t="n">
-        <v>0.965741</v>
+        <v>0.974729</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8433</v>
+        <v>4.1252</v>
       </c>
       <c r="G7" t="n">
-        <v>0.976689</v>
+        <v>0.985783</v>
       </c>
       <c r="H7" t="n">
-        <v>4.6191</v>
+        <v>2.8976</v>
       </c>
       <c r="I7" t="n">
-        <v>0.976689</v>
+        <v>0.985783</v>
       </c>
       <c r="J7" t="n">
-        <v>4.6191</v>
+        <v>2.8976</v>
       </c>
       <c r="K7" t="n">
-        <v>0.96697</v>
+        <v>0.975974</v>
       </c>
       <c r="L7" t="n">
-        <v>6.6285</v>
+        <v>4.9041</v>
       </c>
       <c r="M7" t="n">
-        <v>0.971866</v>
+        <v>0.980915</v>
       </c>
       <c r="N7" t="n">
-        <v>5.6133</v>
+        <v>3.8904</v>
       </c>
       <c r="O7" t="n">
-        <v>0.971769</v>
+        <v>0.980817</v>
       </c>
       <c r="P7" t="n">
-        <v>5.6334</v>
+        <v>3.9104</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9840410000000001</v>
+        <v>0.993204</v>
       </c>
       <c r="R7" t="n">
-        <v>3.1143</v>
+        <v>1.3949</v>
       </c>
       <c r="S7" t="n">
-        <v>0.959745</v>
+        <v>0.968682</v>
       </c>
       <c r="T7" t="n">
-        <v>8.137700000000001</v>
+        <v>6.4111</v>
       </c>
       <c r="U7" t="n">
-        <v>0.982182</v>
+        <v>0.991331</v>
       </c>
       <c r="V7" t="n">
-        <v>4.42</v>
+        <v>2.6941</v>
       </c>
       <c r="W7" t="n">
-        <v>0.961562</v>
+        <v>0.970511</v>
       </c>
       <c r="X7" t="n">
-        <v>6.828</v>
+        <v>5.1079</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.975944</v>
+        <v>0.985036</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.7327</v>
+        <v>4.0048</v>
       </c>
     </row>
     <row r="8">
@@ -1053,76 +1053,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9676090000000001</v>
+        <v>0.977706</v>
       </c>
       <c r="D8" t="n">
-        <v>5.2187</v>
+        <v>3.8785</v>
       </c>
       <c r="E8" t="n">
-        <v>0.961618</v>
+        <v>0.97166</v>
       </c>
       <c r="F8" t="n">
-        <v>5.1446</v>
+        <v>3.7904</v>
       </c>
       <c r="G8" t="n">
-        <v>0.97327</v>
+        <v>0.983426</v>
       </c>
       <c r="H8" t="n">
-        <v>4.2148</v>
+        <v>2.8757</v>
       </c>
       <c r="I8" t="n">
-        <v>0.97327</v>
+        <v>0.983426</v>
       </c>
       <c r="J8" t="n">
-        <v>4.2148</v>
+        <v>2.8757</v>
       </c>
       <c r="K8" t="n">
-        <v>0.961981</v>
+        <v>0.972019</v>
       </c>
       <c r="L8" t="n">
-        <v>6.2235</v>
+        <v>4.8821</v>
       </c>
       <c r="M8" t="n">
-        <v>0.967666</v>
+        <v>0.977763</v>
       </c>
       <c r="N8" t="n">
-        <v>5.2087</v>
+        <v>3.8684</v>
       </c>
       <c r="O8" t="n">
-        <v>0.967553</v>
+        <v>0.977649</v>
       </c>
       <c r="P8" t="n">
-        <v>5.2287</v>
+        <v>3.8885</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.981824</v>
+        <v>0.992069</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7104</v>
+        <v>1.373</v>
       </c>
       <c r="S8" t="n">
-        <v>0.953601</v>
+        <v>0.963551</v>
       </c>
       <c r="T8" t="n">
-        <v>7.7322</v>
+        <v>6.3892</v>
       </c>
       <c r="U8" t="n">
-        <v>0.978693</v>
+        <v>0.9889</v>
       </c>
       <c r="V8" t="n">
-        <v>4.2776</v>
+        <v>2.9509</v>
       </c>
       <c r="W8" t="n">
-        <v>0.956651</v>
+        <v>0.966639</v>
       </c>
       <c r="X8" t="n">
-        <v>6.1605</v>
+        <v>4.8067</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.971411</v>
+        <v>0.981542</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.5996</v>
+        <v>4.2719</v>
       </c>
     </row>
     <row r="9">
@@ -1135,76 +1135,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.963419</v>
+        <v>0.974558</v>
       </c>
       <c r="D9" t="n">
-        <v>5.2187</v>
+        <v>3.8762</v>
       </c>
       <c r="E9" t="n">
-        <v>0.957721</v>
+        <v>0.968793</v>
       </c>
       <c r="F9" t="n">
-        <v>4.884</v>
+        <v>3.5506</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9698639999999999</v>
+        <v>0.981077</v>
       </c>
       <c r="H9" t="n">
-        <v>4.2148</v>
+        <v>2.8734</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9698639999999999</v>
+        <v>0.981077</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2148</v>
+        <v>2.8734</v>
       </c>
       <c r="K9" t="n">
-        <v>0.957018</v>
+        <v>0.968083</v>
       </c>
       <c r="L9" t="n">
-        <v>6.2235</v>
+        <v>4.8798</v>
       </c>
       <c r="M9" t="n">
-        <v>0.963484</v>
+        <v>0.974623</v>
       </c>
       <c r="N9" t="n">
-        <v>5.2087</v>
+        <v>3.8661</v>
       </c>
       <c r="O9" t="n">
-        <v>0.963355</v>
+        <v>0.9744930000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>5.2287</v>
+        <v>3.8862</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.979611</v>
+        <v>0.990937</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7104</v>
+        <v>1.3707</v>
       </c>
       <c r="S9" t="n">
-        <v>0.947495</v>
+        <v>0.95845</v>
       </c>
       <c r="T9" t="n">
-        <v>7.7322</v>
+        <v>6.3869</v>
       </c>
       <c r="U9" t="n">
-        <v>0.975029</v>
+        <v>0.986302</v>
       </c>
       <c r="V9" t="n">
-        <v>4.5099</v>
+        <v>3.1604</v>
       </c>
       <c r="W9" t="n">
-        <v>0.951948</v>
+        <v>0.962954</v>
       </c>
       <c r="X9" t="n">
-        <v>5.9279</v>
+        <v>4.5924</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.966706</v>
+        <v>0.9778829999999999</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.8404</v>
+        <v>4.4891</v>
       </c>
     </row>
     <row r="10">
@@ -1217,76 +1217,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.959248</v>
+        <v>0.971421</v>
       </c>
       <c r="D10" t="n">
-        <v>5.2187</v>
+        <v>3.876</v>
       </c>
       <c r="E10" t="n">
-        <v>0.954019</v>
+        <v>0.966126</v>
       </c>
       <c r="F10" t="n">
-        <v>4.6557</v>
+        <v>3.3133</v>
       </c>
       <c r="G10" t="n">
-        <v>0.966469</v>
+        <v>0.978734</v>
       </c>
       <c r="H10" t="n">
-        <v>4.2148</v>
+        <v>2.8732</v>
       </c>
       <c r="I10" t="n">
-        <v>0.966469</v>
+        <v>0.978734</v>
       </c>
       <c r="J10" t="n">
-        <v>4.2148</v>
+        <v>2.8732</v>
       </c>
       <c r="K10" t="n">
-        <v>0.95208</v>
+        <v>0.964162</v>
       </c>
       <c r="L10" t="n">
-        <v>6.2235</v>
+        <v>4.8796</v>
       </c>
       <c r="M10" t="n">
-        <v>0.95932</v>
+        <v>0.9714930000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>5.2087</v>
+        <v>3.8659</v>
       </c>
       <c r="O10" t="n">
-        <v>0.959176</v>
+        <v>0.971348</v>
       </c>
       <c r="P10" t="n">
-        <v>5.2287</v>
+        <v>3.886</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.977403</v>
+        <v>0.989807</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7105</v>
+        <v>1.3705</v>
       </c>
       <c r="S10" t="n">
-        <v>0.941429</v>
+        <v>0.953376</v>
       </c>
       <c r="T10" t="n">
-        <v>7.7322</v>
+        <v>6.3867</v>
       </c>
       <c r="U10" t="n">
-        <v>0.971214</v>
+        <v>0.9835390000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>4.7135</v>
+        <v>3.3715</v>
       </c>
       <c r="W10" t="n">
-        <v>0.947429</v>
+        <v>0.959452</v>
       </c>
       <c r="X10" t="n">
-        <v>5.7241</v>
+        <v>4.3806</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.961856</v>
+        <v>0.974062</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.0515</v>
+        <v>4.7081</v>
       </c>
     </row>
     <row r="11">
@@ -1299,76 +1299,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.955094</v>
+        <v>0.968293</v>
       </c>
       <c r="D11" t="n">
-        <v>5.2187</v>
+        <v>3.876</v>
       </c>
       <c r="E11" t="n">
-        <v>0.950483</v>
+        <v>0.963619</v>
       </c>
       <c r="F11" t="n">
-        <v>4.4641</v>
+        <v>3.1222</v>
       </c>
       <c r="G11" t="n">
-        <v>0.963086</v>
+        <v>0.976396</v>
       </c>
       <c r="H11" t="n">
-        <v>4.2148</v>
+        <v>2.8732</v>
       </c>
       <c r="I11" t="n">
-        <v>0.963086</v>
+        <v>0.976396</v>
       </c>
       <c r="J11" t="n">
-        <v>4.2148</v>
+        <v>2.8732</v>
       </c>
       <c r="K11" t="n">
-        <v>0.947168</v>
+        <v>0.960257</v>
       </c>
       <c r="L11" t="n">
-        <v>6.2235</v>
+        <v>4.8796</v>
       </c>
       <c r="M11" t="n">
-        <v>0.955174</v>
+        <v>0.968374</v>
       </c>
       <c r="N11" t="n">
-        <v>5.2087</v>
+        <v>3.8659</v>
       </c>
       <c r="O11" t="n">
-        <v>0.955014</v>
+        <v>0.968212</v>
       </c>
       <c r="P11" t="n">
-        <v>5.2288</v>
+        <v>3.886</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.975201</v>
+        <v>0.988677</v>
       </c>
       <c r="R11" t="n">
-        <v>2.7104</v>
+        <v>1.3705</v>
       </c>
       <c r="S11" t="n">
-        <v>0.935402</v>
+        <v>0.948329</v>
       </c>
       <c r="T11" t="n">
-        <v>7.7322</v>
+        <v>6.3867</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9672770000000001</v>
+        <v>0.980644</v>
       </c>
       <c r="V11" t="n">
-        <v>4.8843</v>
+        <v>3.5419</v>
       </c>
       <c r="W11" t="n">
-        <v>0.943065</v>
+        <v>0.956097</v>
       </c>
       <c r="X11" t="n">
-        <v>5.5532</v>
+        <v>4.2101</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.956889</v>
+        <v>0.970113</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.2286</v>
+        <v>4.8847</v>
       </c>
     </row>
     <row r="12">
@@ -1381,76 +1381,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.950958</v>
+        <v>0.965175</v>
       </c>
       <c r="D12" t="n">
-        <v>5.2187</v>
+        <v>3.876</v>
       </c>
       <c r="E12" t="n">
-        <v>0.947093</v>
+        <v>0.961252</v>
       </c>
       <c r="F12" t="n">
-        <v>4.2961</v>
+        <v>2.9544</v>
       </c>
       <c r="G12" t="n">
-        <v>0.959716</v>
+        <v>0.974064</v>
       </c>
       <c r="H12" t="n">
-        <v>4.2148</v>
+        <v>2.8732</v>
       </c>
       <c r="I12" t="n">
-        <v>0.959716</v>
+        <v>0.974064</v>
       </c>
       <c r="J12" t="n">
-        <v>4.2148</v>
+        <v>2.8732</v>
       </c>
       <c r="K12" t="n">
-        <v>0.942281</v>
+        <v>0.956368</v>
       </c>
       <c r="L12" t="n">
-        <v>6.2235</v>
+        <v>4.8796</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9510459999999999</v>
+        <v>0.965264</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2087</v>
+        <v>3.8659</v>
       </c>
       <c r="O12" t="n">
-        <v>0.950871</v>
+        <v>0.965087</v>
       </c>
       <c r="P12" t="n">
-        <v>5.2287</v>
+        <v>3.886</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.973003</v>
+        <v>0.987549</v>
       </c>
       <c r="R12" t="n">
-        <v>2.7104</v>
+        <v>1.3705</v>
       </c>
       <c r="S12" t="n">
-        <v>0.929413</v>
+        <v>0.943308</v>
       </c>
       <c r="T12" t="n">
-        <v>7.7322</v>
+        <v>6.3867</v>
       </c>
       <c r="U12" t="n">
-        <v>0.963236</v>
+        <v>0.977637</v>
       </c>
       <c r="V12" t="n">
-        <v>5.0342</v>
+        <v>3.6917</v>
       </c>
       <c r="W12" t="n">
-        <v>0.938837</v>
+        <v>0.952873</v>
       </c>
       <c r="X12" t="n">
-        <v>5.4032</v>
+        <v>4.0603</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.951825</v>
+        <v>0.966055</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.384</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="13">
@@ -1463,76 +1463,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.946865</v>
+        <v>0.962067</v>
       </c>
       <c r="D13" t="n">
-        <v>5.1879</v>
+        <v>3.8774</v>
       </c>
       <c r="E13" t="n">
-        <v>0.94385</v>
+        <v>0.959004</v>
       </c>
       <c r="F13" t="n">
-        <v>4.1224</v>
+        <v>2.813</v>
       </c>
       <c r="G13" t="n">
-        <v>0.956381</v>
+        <v>0.971736</v>
       </c>
       <c r="H13" t="n">
-        <v>4.184</v>
+        <v>2.8746</v>
       </c>
       <c r="I13" t="n">
-        <v>0.956381</v>
+        <v>0.971736</v>
       </c>
       <c r="J13" t="n">
-        <v>4.184</v>
+        <v>2.8746</v>
       </c>
       <c r="K13" t="n">
-        <v>0.937443</v>
+        <v>0.952494</v>
       </c>
       <c r="L13" t="n">
-        <v>6.1927</v>
+        <v>4.881</v>
       </c>
       <c r="M13" t="n">
-        <v>0.94696</v>
+        <v>0.962163</v>
       </c>
       <c r="N13" t="n">
-        <v>5.1779</v>
+        <v>3.8673</v>
       </c>
       <c r="O13" t="n">
-        <v>0.94677</v>
+        <v>0.961971</v>
       </c>
       <c r="P13" t="n">
-        <v>5.198</v>
+        <v>3.8874</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.970835</v>
+        <v>0.986422</v>
       </c>
       <c r="R13" t="n">
-        <v>2.6797</v>
+        <v>1.3719</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9234869999999999</v>
+        <v>0.938313</v>
       </c>
       <c r="T13" t="n">
-        <v>7.7014</v>
+        <v>6.3881</v>
       </c>
       <c r="U13" t="n">
-        <v>0.959135</v>
+        <v>0.974534</v>
       </c>
       <c r="V13" t="n">
-        <v>5.131</v>
+        <v>3.8205</v>
       </c>
       <c r="W13" t="n">
-        <v>0.934752</v>
+        <v>0.949759</v>
       </c>
       <c r="X13" t="n">
-        <v>5.2449</v>
+        <v>3.9343</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.946709</v>
+        <v>0.961908</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.4855</v>
+        <v>5.1735</v>
       </c>
     </row>
     <row r="14">
@@ -1545,76 +1545,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.925861</v>
+        <v>0.942833</v>
       </c>
       <c r="D14" t="n">
-        <v>5.1576</v>
+        <v>4.0457</v>
       </c>
       <c r="E14" t="n">
-        <v>0.929329</v>
+        <v>0.946364</v>
       </c>
       <c r="F14" t="n">
-        <v>3.6082</v>
+        <v>2.4988</v>
       </c>
       <c r="G14" t="n">
-        <v>0.939854</v>
+        <v>0.957082</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1537</v>
+        <v>3.0428</v>
       </c>
       <c r="I14" t="n">
-        <v>0.939854</v>
+        <v>0.957082</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1537</v>
+        <v>3.0428</v>
       </c>
       <c r="K14" t="n">
-        <v>0.912077</v>
+        <v>0.928796</v>
       </c>
       <c r="L14" t="n">
-        <v>6.1623</v>
+        <v>5.0495</v>
       </c>
       <c r="M14" t="n">
-        <v>0.926</v>
+        <v>0.942975</v>
       </c>
       <c r="N14" t="n">
-        <v>5.1475</v>
+        <v>4.0357</v>
       </c>
       <c r="O14" t="n">
-        <v>0.925722</v>
+        <v>0.942692</v>
       </c>
       <c r="P14" t="n">
-        <v>5.1676</v>
+        <v>4.0558</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.96124</v>
+        <v>0.978861</v>
       </c>
       <c r="R14" t="n">
-        <v>2.6494</v>
+        <v>1.5399</v>
       </c>
       <c r="S14" t="n">
-        <v>0.891784</v>
+        <v>0.9081320000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>7.6709</v>
+        <v>6.5568</v>
       </c>
       <c r="U14" t="n">
-        <v>0.93677</v>
+        <v>0.953943</v>
       </c>
       <c r="V14" t="n">
-        <v>5.5327</v>
+        <v>4.4196</v>
       </c>
       <c r="W14" t="n">
-        <v>0.915079</v>
+        <v>0.931853</v>
       </c>
       <c r="X14" t="n">
-        <v>4.7826</v>
+        <v>3.672</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.9183750000000001</v>
+        <v>0.935211</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.9031</v>
+        <v>5.7887</v>
       </c>
     </row>
     <row r="15">
@@ -1627,76 +1627,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.902322</v>
+        <v>0.923984</v>
       </c>
       <c r="D15" t="n">
-        <v>5.1643</v>
+        <v>4.0457</v>
       </c>
       <c r="E15" t="n">
-        <v>0.913102</v>
+        <v>0.935023</v>
       </c>
       <c r="F15" t="n">
-        <v>3.5028</v>
+        <v>2.3857</v>
       </c>
       <c r="G15" t="n">
-        <v>0.920551</v>
+        <v>0.94265</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1604</v>
+        <v>3.0428</v>
       </c>
       <c r="I15" t="n">
-        <v>0.920551</v>
+        <v>0.94265</v>
       </c>
       <c r="J15" t="n">
-        <v>4.1604</v>
+        <v>3.0428</v>
       </c>
       <c r="K15" t="n">
-        <v>0.884455</v>
+        <v>0.905688</v>
       </c>
       <c r="L15" t="n">
-        <v>6.169</v>
+        <v>5.0495</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9025030000000001</v>
+        <v>0.924169</v>
       </c>
       <c r="N15" t="n">
-        <v>5.1542</v>
+        <v>4.0357</v>
       </c>
       <c r="O15" t="n">
-        <v>0.902142</v>
+        <v>0.923799</v>
       </c>
       <c r="P15" t="n">
-        <v>5.1743</v>
+        <v>4.0558</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.948585</v>
+        <v>0.9713580000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>2.6561</v>
+        <v>1.5399</v>
       </c>
       <c r="S15" t="n">
-        <v>0.858316</v>
+        <v>0.878921</v>
       </c>
       <c r="T15" t="n">
-        <v>7.6776</v>
+        <v>6.5568</v>
       </c>
       <c r="U15" t="n">
-        <v>0.910911</v>
+        <v>0.932779</v>
       </c>
       <c r="V15" t="n">
-        <v>5.6394</v>
+        <v>4.5205</v>
       </c>
       <c r="W15" t="n">
-        <v>0.893815</v>
+        <v>0.915272</v>
       </c>
       <c r="X15" t="n">
-        <v>4.6892</v>
+        <v>3.5711</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.886946</v>
+        <v>0.908238</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.0135</v>
+        <v>5.8934</v>
       </c>
     </row>
     <row r="16">
@@ -1709,76 +1709,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.879355</v>
+        <v>0.906675</v>
       </c>
       <c r="D16" t="n">
-        <v>5.1703</v>
+        <v>3.786</v>
       </c>
       <c r="E16" t="n">
-        <v>0.897182</v>
+        <v>0.925055</v>
       </c>
       <c r="F16" t="n">
-        <v>3.5498</v>
+        <v>2.1677</v>
       </c>
       <c r="G16" t="n">
-        <v>0.901616</v>
+        <v>0.929628</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1664</v>
+        <v>2.7833</v>
       </c>
       <c r="I16" t="n">
-        <v>0.901616</v>
+        <v>0.929628</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1664</v>
+        <v>2.7833</v>
       </c>
       <c r="K16" t="n">
-        <v>0.857643</v>
+        <v>0.884289</v>
       </c>
       <c r="L16" t="n">
-        <v>6.175</v>
+        <v>4.7896</v>
       </c>
       <c r="M16" t="n">
-        <v>0.879574</v>
+        <v>0.906902</v>
       </c>
       <c r="N16" t="n">
-        <v>5.1602</v>
+        <v>3.776</v>
       </c>
       <c r="O16" t="n">
-        <v>0.879135</v>
+        <v>0.906448</v>
       </c>
       <c r="P16" t="n">
-        <v>5.1803</v>
+        <v>3.796</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.936068</v>
+        <v>0.96515</v>
       </c>
       <c r="R16" t="n">
-        <v>2.6621</v>
+        <v>1.2807</v>
       </c>
       <c r="S16" t="n">
-        <v>0.826077</v>
+        <v>0.851742</v>
       </c>
       <c r="T16" t="n">
-        <v>7.6837</v>
+        <v>6.2965</v>
       </c>
       <c r="U16" t="n">
-        <v>0.885694</v>
+        <v>0.913211</v>
       </c>
       <c r="V16" t="n">
-        <v>5.6089</v>
+        <v>4.2237</v>
       </c>
       <c r="W16" t="n">
-        <v>0.873061</v>
+        <v>0.900186</v>
       </c>
       <c r="X16" t="n">
-        <v>4.7319</v>
+        <v>3.3484</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.8565199999999999</v>
+        <v>0.883131</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.9816</v>
+        <v>5.5949</v>
       </c>
     </row>
     <row r="17">
@@ -1791,76 +1791,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.856947</v>
+        <v>0.8897</v>
       </c>
       <c r="D17" t="n">
-        <v>5.1757</v>
+        <v>3.786</v>
       </c>
       <c r="E17" t="n">
-        <v>0.881182</v>
+        <v>0.91486</v>
       </c>
       <c r="F17" t="n">
-        <v>3.646</v>
+        <v>2.2587</v>
       </c>
       <c r="G17" t="n">
-        <v>0.883045</v>
+        <v>0.916795</v>
       </c>
       <c r="H17" t="n">
-        <v>4.1718</v>
+        <v>2.7833</v>
       </c>
       <c r="I17" t="n">
-        <v>0.883045</v>
+        <v>0.916795</v>
       </c>
       <c r="J17" t="n">
-        <v>4.1718</v>
+        <v>2.7833</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8316210000000001</v>
+        <v>0.863405</v>
       </c>
       <c r="L17" t="n">
-        <v>6.1804</v>
+        <v>4.7896</v>
       </c>
       <c r="M17" t="n">
-        <v>0.857205</v>
+        <v>0.889967</v>
       </c>
       <c r="N17" t="n">
-        <v>5.1656</v>
+        <v>3.776</v>
       </c>
       <c r="O17" t="n">
-        <v>0.85669</v>
+        <v>0.889433</v>
       </c>
       <c r="P17" t="n">
-        <v>5.1857</v>
+        <v>3.796</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.92369</v>
+        <v>0.958993</v>
       </c>
       <c r="R17" t="n">
-        <v>2.6675</v>
+        <v>1.2807</v>
       </c>
       <c r="S17" t="n">
-        <v>0.795027</v>
+        <v>0.825413</v>
       </c>
       <c r="T17" t="n">
-        <v>7.6891</v>
+        <v>6.2965</v>
       </c>
       <c r="U17" t="n">
-        <v>0.861439</v>
+        <v>0.894363</v>
       </c>
       <c r="V17" t="n">
-        <v>5.5332</v>
+        <v>4.1425</v>
       </c>
       <c r="W17" t="n">
-        <v>0.852479</v>
+        <v>0.88506</v>
       </c>
       <c r="X17" t="n">
-        <v>4.8183</v>
+        <v>3.4296</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.827402</v>
+        <v>0.859026</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.9029</v>
+        <v>5.5106</v>
       </c>
     </row>
     <row r="18">
@@ -1873,76 +1873,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.83509</v>
+        <v>0.873042</v>
       </c>
       <c r="D18" t="n">
-        <v>5.1805</v>
+        <v>3.7861</v>
       </c>
       <c r="E18" t="n">
-        <v>0.865031</v>
+        <v>0.904344</v>
       </c>
       <c r="F18" t="n">
-        <v>3.7465</v>
+        <v>2.3537</v>
       </c>
       <c r="G18" t="n">
-        <v>0.864836</v>
+        <v>0.904139</v>
       </c>
       <c r="H18" t="n">
-        <v>4.1766</v>
+        <v>2.7833</v>
       </c>
       <c r="I18" t="n">
-        <v>0.864836</v>
+        <v>0.904139</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1766</v>
+        <v>2.7833</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8063669999999999</v>
+        <v>0.843014</v>
       </c>
       <c r="L18" t="n">
-        <v>6.1853</v>
+        <v>4.7897</v>
       </c>
       <c r="M18" t="n">
-        <v>0.835382</v>
+        <v>0.873347</v>
       </c>
       <c r="N18" t="n">
-        <v>5.1705</v>
+        <v>3.7761</v>
       </c>
       <c r="O18" t="n">
-        <v>0.834798</v>
+        <v>0.872736</v>
       </c>
       <c r="P18" t="n">
-        <v>5.1906</v>
+        <v>3.7961</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.911452</v>
+        <v>0.952875</v>
       </c>
       <c r="R18" t="n">
-        <v>2.6724</v>
+        <v>1.2808</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7651250000000001</v>
+        <v>0.799897</v>
       </c>
       <c r="T18" t="n">
-        <v>7.6939</v>
+        <v>6.2966</v>
       </c>
       <c r="U18" t="n">
-        <v>0.838185</v>
+        <v>0.876277</v>
       </c>
       <c r="V18" t="n">
-        <v>5.4525</v>
+        <v>4.0577</v>
       </c>
       <c r="W18" t="n">
-        <v>0.832006</v>
+        <v>0.869818</v>
       </c>
       <c r="X18" t="n">
-        <v>4.9086</v>
+        <v>3.5145</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.799608</v>
+        <v>0.835947</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.8192</v>
+        <v>5.4228</v>
       </c>
     </row>
     <row r="19">
@@ -1955,76 +1955,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.8137720000000001</v>
+        <v>0.856691</v>
       </c>
       <c r="D19" t="n">
-        <v>5.1849</v>
+        <v>3.7918</v>
       </c>
       <c r="E19" t="n">
-        <v>0.848783</v>
+        <v>0.89355</v>
       </c>
       <c r="F19" t="n">
-        <v>3.8334</v>
+        <v>2.4417</v>
       </c>
       <c r="G19" t="n">
-        <v>0.846982</v>
+        <v>0.8916539999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>4.181</v>
+        <v>2.7891</v>
       </c>
       <c r="I19" t="n">
-        <v>0.846982</v>
+        <v>0.8916539999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>4.181</v>
+        <v>2.7891</v>
       </c>
       <c r="K19" t="n">
-        <v>0.781863</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>6.1896</v>
+        <v>4.7954</v>
       </c>
       <c r="M19" t="n">
-        <v>0.814097</v>
+        <v>0.857034</v>
       </c>
       <c r="N19" t="n">
-        <v>5.1749</v>
+        <v>3.7818</v>
       </c>
       <c r="O19" t="n">
-        <v>0.813446</v>
+        <v>0.856349</v>
       </c>
       <c r="P19" t="n">
-        <v>5.1949</v>
+        <v>3.8018</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.899357</v>
+        <v>0.946791</v>
       </c>
       <c r="R19" t="n">
-        <v>2.6767</v>
+        <v>1.2865</v>
       </c>
       <c r="S19" t="n">
-        <v>0.736331</v>
+        <v>0.775166</v>
       </c>
       <c r="T19" t="n">
-        <v>7.6983</v>
+        <v>6.3023</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8158609999999999</v>
+        <v>0.858891</v>
       </c>
       <c r="V19" t="n">
-        <v>5.3832</v>
+        <v>3.9901</v>
       </c>
       <c r="W19" t="n">
-        <v>0.811687</v>
+        <v>0.854497</v>
       </c>
       <c r="X19" t="n">
-        <v>4.9866</v>
+        <v>3.5936</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.773044</v>
+        <v>0.813816</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.7472</v>
+        <v>5.3524</v>
       </c>
     </row>
     <row r="20">
@@ -2037,76 +2037,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.792981</v>
+        <v>0.8398870000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>5.1888</v>
+        <v>3.9697</v>
       </c>
       <c r="E20" t="n">
-        <v>0.832524</v>
+        <v>0.881769</v>
       </c>
       <c r="F20" t="n">
-        <v>3.9017</v>
+        <v>2.6835</v>
       </c>
       <c r="G20" t="n">
-        <v>0.829481</v>
+        <v>0.878545</v>
       </c>
       <c r="H20" t="n">
-        <v>4.1849</v>
+        <v>2.9668</v>
       </c>
       <c r="I20" t="n">
-        <v>0.829481</v>
+        <v>0.878545</v>
       </c>
       <c r="J20" t="n">
-        <v>4.1849</v>
+        <v>2.9668</v>
       </c>
       <c r="K20" t="n">
-        <v>0.758088</v>
+        <v>0.80293</v>
       </c>
       <c r="L20" t="n">
-        <v>6.1935</v>
+        <v>4.9734</v>
       </c>
       <c r="M20" t="n">
-        <v>0.793338</v>
+        <v>0.840265</v>
       </c>
       <c r="N20" t="n">
-        <v>5.1787</v>
+        <v>3.9597</v>
       </c>
       <c r="O20" t="n">
-        <v>0.792625</v>
+        <v>0.8395089999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>5.1988</v>
+        <v>3.9797</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8874030000000001</v>
+        <v>0.939894</v>
       </c>
       <c r="R20" t="n">
-        <v>2.6806</v>
+        <v>1.464</v>
       </c>
       <c r="S20" t="n">
-        <v>0.708606</v>
+        <v>0.750521</v>
       </c>
       <c r="T20" t="n">
-        <v>7.7022</v>
+        <v>6.4806</v>
       </c>
       <c r="U20" t="n">
-        <v>0.79437</v>
+        <v>0.8413580000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>5.3296</v>
+        <v>4.1107</v>
       </c>
       <c r="W20" t="n">
-        <v>0.791595</v>
+        <v>0.838418</v>
       </c>
       <c r="X20" t="n">
-        <v>5.048</v>
+        <v>3.8287</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.747595</v>
+        <v>0.791816</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.6914</v>
+        <v>5.4711</v>
       </c>
     </row>
     <row r="21">
@@ -2119,76 +2119,76 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.772708</v>
+        <v>0.823406</v>
       </c>
       <c r="D21" t="n">
-        <v>5.1923</v>
+        <v>3.9721</v>
       </c>
       <c r="E21" t="n">
-        <v>0.816338</v>
+        <v>0.869899</v>
       </c>
       <c r="F21" t="n">
-        <v>3.9534</v>
+        <v>2.7344</v>
       </c>
       <c r="G21" t="n">
-        <v>0.812326</v>
+        <v>0.865623</v>
       </c>
       <c r="H21" t="n">
-        <v>4.1884</v>
+        <v>2.9692</v>
       </c>
       <c r="I21" t="n">
-        <v>0.812326</v>
+        <v>0.865623</v>
       </c>
       <c r="J21" t="n">
-        <v>4.1884</v>
+        <v>2.9692</v>
       </c>
       <c r="K21" t="n">
-        <v>0.735023</v>
+        <v>0.7832480000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>6.197</v>
+        <v>4.9758</v>
       </c>
       <c r="M21" t="n">
-        <v>0.773095</v>
+        <v>0.8238180000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>5.1822</v>
+        <v>3.962</v>
       </c>
       <c r="O21" t="n">
-        <v>0.772322</v>
+        <v>0.822994</v>
       </c>
       <c r="P21" t="n">
-        <v>5.2023</v>
+        <v>3.9821</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.875593</v>
+        <v>0.933041</v>
       </c>
       <c r="R21" t="n">
-        <v>2.6841</v>
+        <v>1.4664</v>
       </c>
       <c r="S21" t="n">
-        <v>0.681913</v>
+        <v>0.726653</v>
       </c>
       <c r="T21" t="n">
-        <v>7.7057</v>
+        <v>6.483</v>
       </c>
       <c r="U21" t="n">
-        <v>0.77362</v>
+        <v>0.824377</v>
       </c>
       <c r="V21" t="n">
-        <v>5.2901</v>
+        <v>4.0698</v>
       </c>
       <c r="W21" t="n">
-        <v>0.771797</v>
+        <v>0.8224359999999999</v>
       </c>
       <c r="X21" t="n">
-        <v>5.0945</v>
+        <v>3.8744</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.723154</v>
+        <v>0.770601</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.6503</v>
+        <v>5.4286</v>
       </c>
     </row>
     <row r="22">
@@ -2201,76 +2201,76 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.733669</v>
+        <v>0.789117</v>
       </c>
       <c r="D22" t="n">
-        <v>5.1982</v>
+        <v>4.261</v>
       </c>
       <c r="E22" t="n">
-        <v>0.784443</v>
+        <v>0.843729</v>
       </c>
       <c r="F22" t="n">
-        <v>4.0184</v>
+        <v>3.082</v>
       </c>
       <c r="G22" t="n">
-        <v>0.779036</v>
+        <v>0.837914</v>
       </c>
       <c r="H22" t="n">
-        <v>4.1943</v>
+        <v>3.2578</v>
       </c>
       <c r="I22" t="n">
-        <v>0.779036</v>
+        <v>0.837914</v>
       </c>
       <c r="J22" t="n">
-        <v>4.1943</v>
+        <v>3.2578</v>
       </c>
       <c r="K22" t="n">
-        <v>0.690943</v>
+        <v>0.743163</v>
       </c>
       <c r="L22" t="n">
-        <v>6.203</v>
+        <v>5.2649</v>
       </c>
       <c r="M22" t="n">
-        <v>0.734109</v>
+        <v>0.789591</v>
       </c>
       <c r="N22" t="n">
-        <v>5.1882</v>
+        <v>4.2509</v>
       </c>
       <c r="O22" t="n">
-        <v>0.733229</v>
+        <v>0.788644</v>
       </c>
       <c r="P22" t="n">
-        <v>5.2083</v>
+        <v>4.271</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.852401</v>
+        <v>0.916824</v>
       </c>
       <c r="R22" t="n">
-        <v>2.69</v>
+        <v>1.7547</v>
       </c>
       <c r="S22" t="n">
-        <v>0.631474</v>
+        <v>0.6792</v>
       </c>
       <c r="T22" t="n">
-        <v>7.7117</v>
+        <v>6.7725</v>
       </c>
       <c r="U22" t="n">
-        <v>0.734051</v>
+        <v>0.789528</v>
       </c>
       <c r="V22" t="n">
-        <v>5.2433</v>
+        <v>4.306</v>
       </c>
       <c r="W22" t="n">
-        <v>0.733287</v>
+        <v>0.788707</v>
       </c>
       <c r="X22" t="n">
-        <v>5.1531</v>
+        <v>4.2159</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.676949</v>
+        <v>0.728112</v>
       </c>
       <c r="Z22" t="n">
-        <v>6.6016</v>
+        <v>5.6632</v>
       </c>
     </row>
     <row r="23">
@@ -2283,76 +2283,76 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.696565</v>
+        <v>0.756257</v>
       </c>
       <c r="D23" t="n">
-        <v>5.203</v>
+        <v>4.261</v>
       </c>
       <c r="E23" t="n">
-        <v>0.753448</v>
+        <v>0.818015</v>
       </c>
       <c r="F23" t="n">
-        <v>4.0513</v>
+        <v>3.1102</v>
       </c>
       <c r="G23" t="n">
-        <v>0.747072</v>
+        <v>0.811092</v>
       </c>
       <c r="H23" t="n">
-        <v>4.1991</v>
+        <v>3.2578</v>
       </c>
       <c r="I23" t="n">
-        <v>0.747072</v>
+        <v>0.811092</v>
       </c>
       <c r="J23" t="n">
-        <v>4.1991</v>
+        <v>3.2578</v>
       </c>
       <c r="K23" t="n">
-        <v>0.649473</v>
+        <v>0.705129</v>
       </c>
       <c r="L23" t="n">
-        <v>6.2077</v>
+        <v>5.2649</v>
       </c>
       <c r="M23" t="n">
-        <v>0.697053</v>
+        <v>0.756786</v>
       </c>
       <c r="N23" t="n">
-        <v>5.1929</v>
+        <v>4.2509</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6960769999999999</v>
+        <v>0.755728</v>
       </c>
       <c r="P23" t="n">
-        <v>5.213</v>
+        <v>4.271</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.82978</v>
+        <v>0.900888</v>
       </c>
       <c r="R23" t="n">
-        <v>2.6948</v>
+        <v>1.7547</v>
       </c>
       <c r="S23" t="n">
-        <v>0.584736</v>
+        <v>0.634845</v>
       </c>
       <c r="T23" t="n">
-        <v>7.7164</v>
+        <v>6.7725</v>
       </c>
       <c r="U23" t="n">
-        <v>0.696721</v>
+        <v>0.756426</v>
       </c>
       <c r="V23" t="n">
-        <v>5.2229</v>
+        <v>4.2809</v>
       </c>
       <c r="W23" t="n">
-        <v>0.6964089999999999</v>
+        <v>0.756088</v>
       </c>
       <c r="X23" t="n">
-        <v>5.1831</v>
+        <v>4.2411</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.633901</v>
+        <v>0.688223</v>
       </c>
       <c r="Z23" t="n">
-        <v>6.5802</v>
+        <v>5.6372</v>
       </c>
     </row>
     <row r="24">
@@ -2365,76 +2365,76 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.66131</v>
+        <v>0.722263</v>
       </c>
       <c r="D24" t="n">
-        <v>5.2068</v>
+        <v>4.6102</v>
       </c>
       <c r="E24" t="n">
-        <v>0.723512</v>
+        <v>0.790198</v>
       </c>
       <c r="F24" t="n">
-        <v>4.0678</v>
+        <v>3.4718</v>
       </c>
       <c r="G24" t="n">
-        <v>0.716388</v>
+        <v>0.7824179999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>4.2028</v>
+        <v>3.6067</v>
       </c>
       <c r="I24" t="n">
-        <v>0.716388</v>
+        <v>0.7824179999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>4.2028</v>
+        <v>3.6067</v>
       </c>
       <c r="K24" t="n">
-        <v>0.610466</v>
+        <v>0.666733</v>
       </c>
       <c r="L24" t="n">
-        <v>6.2115</v>
+        <v>5.6144</v>
       </c>
       <c r="M24" t="n">
-        <v>0.661839</v>
+        <v>0.722841</v>
       </c>
       <c r="N24" t="n">
-        <v>5.1967</v>
+        <v>4.6001</v>
       </c>
       <c r="O24" t="n">
-        <v>0.660781</v>
+        <v>0.721685</v>
       </c>
       <c r="P24" t="n">
-        <v>5.2168</v>
+        <v>4.6202</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.8077260000000001</v>
+        <v>0.882174</v>
       </c>
       <c r="R24" t="n">
-        <v>2.6985</v>
+        <v>2.1032</v>
       </c>
       <c r="S24" t="n">
-        <v>0.541435</v>
+        <v>0.5913389999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>7.7202</v>
+        <v>7.1224</v>
       </c>
       <c r="U24" t="n">
-        <v>0.661372</v>
+        <v>0.7223309999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>5.2153</v>
+        <v>4.6187</v>
       </c>
       <c r="W24" t="n">
-        <v>0.6612479999999999</v>
+        <v>0.722195</v>
       </c>
       <c r="X24" t="n">
-        <v>5.1982</v>
+        <v>4.6016</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.593668</v>
+        <v>0.648386</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.5723</v>
+        <v>5.975</v>
       </c>
     </row>
     <row r="25">
@@ -2447,76 +2447,76 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.627818</v>
+        <v>0.689782</v>
       </c>
       <c r="D25" t="n">
-        <v>5.2098</v>
+        <v>4.6102</v>
       </c>
       <c r="E25" t="n">
-        <v>0.694684</v>
+        <v>0.763247</v>
       </c>
       <c r="F25" t="n">
-        <v>4.0764</v>
+        <v>3.4774</v>
       </c>
       <c r="G25" t="n">
-        <v>0.686943</v>
+        <v>0.754742</v>
       </c>
       <c r="H25" t="n">
-        <v>4.2059</v>
+        <v>3.6068</v>
       </c>
       <c r="I25" t="n">
-        <v>0.686943</v>
+        <v>0.754742</v>
       </c>
       <c r="J25" t="n">
-        <v>4.2059</v>
+        <v>3.6068</v>
       </c>
       <c r="K25" t="n">
-        <v>0.573783</v>
+        <v>0.630413</v>
       </c>
       <c r="L25" t="n">
-        <v>6.2145</v>
+        <v>5.6144</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6283840000000001</v>
+        <v>0.690403</v>
       </c>
       <c r="N25" t="n">
-        <v>5.1997</v>
+        <v>4.6001</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6272529999999999</v>
+        <v>0.689161</v>
       </c>
       <c r="P25" t="n">
-        <v>5.2198</v>
+        <v>4.6202</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.786231</v>
+        <v>0.86383</v>
       </c>
       <c r="R25" t="n">
-        <v>2.7016</v>
+        <v>2.1032</v>
       </c>
       <c r="S25" t="n">
-        <v>0.501323</v>
+        <v>0.550802</v>
       </c>
       <c r="T25" t="n">
-        <v>7.7233</v>
+        <v>7.1224</v>
       </c>
       <c r="U25" t="n">
-        <v>0.627843</v>
+        <v>0.689809</v>
       </c>
       <c r="V25" t="n">
-        <v>5.2134</v>
+        <v>4.6138</v>
       </c>
       <c r="W25" t="n">
-        <v>0.627794</v>
+        <v>0.689755</v>
       </c>
       <c r="X25" t="n">
-        <v>5.2062</v>
+        <v>4.6066</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.556013</v>
+        <v>0.610889</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.5701</v>
+        <v>5.9699</v>
       </c>
     </row>
     <row r="26">
@@ -2529,76 +2529,76 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.596007</v>
+        <v>0.658762</v>
       </c>
       <c r="D26" t="n">
-        <v>5.2122</v>
+        <v>4.6102</v>
       </c>
       <c r="E26" t="n">
-        <v>0.666963</v>
+        <v>0.737189</v>
       </c>
       <c r="F26" t="n">
-        <v>4.0811</v>
+        <v>3.4797</v>
       </c>
       <c r="G26" t="n">
-        <v>0.658689</v>
+        <v>0.728044</v>
       </c>
       <c r="H26" t="n">
-        <v>4.2082</v>
+        <v>3.6068</v>
       </c>
       <c r="I26" t="n">
-        <v>0.658689</v>
+        <v>0.728044</v>
       </c>
       <c r="J26" t="n">
-        <v>4.2082</v>
+        <v>3.6068</v>
       </c>
       <c r="K26" t="n">
-        <v>0.539289</v>
+        <v>0.596072</v>
       </c>
       <c r="L26" t="n">
-        <v>6.2169</v>
+        <v>5.6144</v>
       </c>
       <c r="M26" t="n">
-        <v>0.596603</v>
+        <v>0.659421</v>
       </c>
       <c r="N26" t="n">
-        <v>5.2021</v>
+        <v>4.6002</v>
       </c>
       <c r="O26" t="n">
-        <v>0.595411</v>
+        <v>0.658103</v>
       </c>
       <c r="P26" t="n">
-        <v>5.2222</v>
+        <v>4.6202</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.765288</v>
+        <v>0.845867</v>
       </c>
       <c r="R26" t="n">
-        <v>2.7039</v>
+        <v>2.1032</v>
       </c>
       <c r="S26" t="n">
-        <v>0.464171</v>
+        <v>0.5130439999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>7.7257</v>
+        <v>7.1224</v>
       </c>
       <c r="U26" t="n">
-        <v>0.596016</v>
+        <v>0.658772</v>
       </c>
       <c r="V26" t="n">
-        <v>5.2137</v>
+        <v>4.6117</v>
       </c>
       <c r="W26" t="n">
-        <v>0.595997</v>
+        <v>0.658751</v>
       </c>
       <c r="X26" t="n">
-        <v>5.2107</v>
+        <v>4.6087</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.520749</v>
+        <v>0.57558</v>
       </c>
       <c r="Z26" t="n">
-        <v>6.5703</v>
+        <v>5.9677</v>
       </c>
     </row>
     <row r="27">
@@ -2611,76 +2611,76 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.459447</v>
+        <v>0.5158</v>
       </c>
       <c r="D27" t="n">
-        <v>5.2183</v>
+        <v>4.9772</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5439040000000001</v>
+        <v>0.610617</v>
       </c>
       <c r="F27" t="n">
-        <v>4.0889</v>
+        <v>3.848</v>
       </c>
       <c r="G27" t="n">
-        <v>0.533801</v>
+        <v>0.599274</v>
       </c>
       <c r="H27" t="n">
-        <v>4.2143</v>
+        <v>3.9734</v>
       </c>
       <c r="I27" t="n">
-        <v>0.533801</v>
+        <v>0.599274</v>
       </c>
       <c r="J27" t="n">
-        <v>4.2143</v>
+        <v>3.9734</v>
       </c>
       <c r="K27" t="n">
-        <v>0.395449</v>
+        <v>0.443953</v>
       </c>
       <c r="L27" t="n">
-        <v>6.223</v>
+        <v>5.9817</v>
       </c>
       <c r="M27" t="n">
-        <v>0.460136</v>
+        <v>0.516575</v>
       </c>
       <c r="N27" t="n">
-        <v>5.2082</v>
+        <v>4.9671</v>
       </c>
       <c r="O27" t="n">
-        <v>0.458758</v>
+        <v>0.515027</v>
       </c>
       <c r="P27" t="n">
-        <v>5.2283</v>
+        <v>4.9872</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.6684909999999999</v>
+        <v>0.750485</v>
       </c>
       <c r="R27" t="n">
-        <v>2.71</v>
+        <v>2.4694</v>
       </c>
       <c r="S27" t="n">
-        <v>0.315773</v>
+        <v>0.354504</v>
       </c>
       <c r="T27" t="n">
-        <v>7.7317</v>
+        <v>7.4902</v>
       </c>
       <c r="U27" t="n">
-        <v>0.459447</v>
+        <v>0.5158</v>
       </c>
       <c r="V27" t="n">
-        <v>5.2183</v>
+        <v>4.9772</v>
       </c>
       <c r="W27" t="n">
-        <v>0.459447</v>
+        <v>0.5158</v>
       </c>
       <c r="X27" t="n">
-        <v>5.2183</v>
+        <v>4.9772</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.375224</v>
+        <v>0.421247</v>
       </c>
       <c r="Z27" t="n">
-        <v>6.5749</v>
+        <v>6.3336</v>
       </c>
     </row>
     <row r="28">
@@ -2693,76 +2693,76 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.354117</v>
+        <v>0.40181</v>
       </c>
       <c r="D28" t="n">
-        <v>5.2198</v>
+        <v>5.0173</v>
       </c>
       <c r="E28" t="n">
-        <v>0.443469</v>
+        <v>0.5031949999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>4.0904</v>
+        <v>3.8881</v>
       </c>
       <c r="G28" t="n">
-        <v>0.43252</v>
+        <v>0.490771</v>
       </c>
       <c r="H28" t="n">
-        <v>4.2158</v>
+        <v>4.0135</v>
       </c>
       <c r="I28" t="n">
-        <v>0.43252</v>
+        <v>0.490771</v>
       </c>
       <c r="J28" t="n">
-        <v>4.2158</v>
+        <v>4.0135</v>
       </c>
       <c r="K28" t="n">
-        <v>0.289926</v>
+        <v>0.328974</v>
       </c>
       <c r="L28" t="n">
-        <v>6.2245</v>
+        <v>6.0219</v>
       </c>
       <c r="M28" t="n">
-        <v>0.354826</v>
+        <v>0.402614</v>
       </c>
       <c r="N28" t="n">
-        <v>5.2097</v>
+        <v>5.0072</v>
       </c>
       <c r="O28" t="n">
-        <v>0.353409</v>
+        <v>0.401007</v>
       </c>
       <c r="P28" t="n">
-        <v>5.2298</v>
+        <v>5.0273</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.58384</v>
+        <v>0.6624719999999999</v>
       </c>
       <c r="R28" t="n">
-        <v>2.7115</v>
+        <v>2.5094</v>
       </c>
       <c r="S28" t="n">
-        <v>0.214783</v>
+        <v>0.24371</v>
       </c>
       <c r="T28" t="n">
-        <v>7.7332</v>
+        <v>7.5303</v>
       </c>
       <c r="U28" t="n">
-        <v>0.354117</v>
+        <v>0.40181</v>
       </c>
       <c r="V28" t="n">
-        <v>5.2198</v>
+        <v>5.0173</v>
       </c>
       <c r="W28" t="n">
-        <v>0.354117</v>
+        <v>0.40181</v>
       </c>
       <c r="X28" t="n">
-        <v>5.2198</v>
+        <v>5.0173</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.270326</v>
+        <v>0.306733</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.5764</v>
+        <v>6.3736</v>
       </c>
     </row>
     <row r="29">
@@ -2775,76 +2775,76 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.272926</v>
+        <v>0.312939</v>
       </c>
       <c r="D29" t="n">
-        <v>5.2199</v>
+        <v>4.9972</v>
       </c>
       <c r="E29" t="n">
-        <v>0.361568</v>
+        <v>0.414577</v>
       </c>
       <c r="F29" t="n">
-        <v>4.0905</v>
+        <v>3.868</v>
       </c>
       <c r="G29" t="n">
-        <v>0.350444</v>
+        <v>0.401821</v>
       </c>
       <c r="H29" t="n">
-        <v>4.2159</v>
+        <v>3.9934</v>
       </c>
       <c r="I29" t="n">
-        <v>0.350444</v>
+        <v>0.401821</v>
       </c>
       <c r="J29" t="n">
-        <v>4.2159</v>
+        <v>3.9934</v>
       </c>
       <c r="K29" t="n">
-        <v>0.212555</v>
+        <v>0.243717</v>
       </c>
       <c r="L29" t="n">
-        <v>6.2247</v>
+        <v>6.0017</v>
       </c>
       <c r="M29" t="n">
-        <v>0.273609</v>
+        <v>0.313722</v>
       </c>
       <c r="N29" t="n">
-        <v>5.2099</v>
+        <v>4.9871</v>
       </c>
       <c r="O29" t="n">
-        <v>0.272244</v>
+        <v>0.312157</v>
       </c>
       <c r="P29" t="n">
-        <v>5.2299</v>
+        <v>5.0072</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.509892</v>
+        <v>0.584647</v>
       </c>
       <c r="R29" t="n">
-        <v>2.7116</v>
+        <v>2.4893</v>
       </c>
       <c r="S29" t="n">
-        <v>0.146087</v>
+        <v>0.167504</v>
       </c>
       <c r="T29" t="n">
-        <v>7.7334</v>
+        <v>7.5102</v>
       </c>
       <c r="U29" t="n">
-        <v>0.272926</v>
+        <v>0.312939</v>
       </c>
       <c r="V29" t="n">
-        <v>5.2199</v>
+        <v>4.9972</v>
       </c>
       <c r="W29" t="n">
-        <v>0.272926</v>
+        <v>0.312939</v>
       </c>
       <c r="X29" t="n">
-        <v>5.2199</v>
+        <v>4.9972</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.194747</v>
+        <v>0.223298</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.5765</v>
+        <v>6.3535</v>
       </c>
     </row>
     <row r="30">
@@ -2857,76 +2857,76 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.210366</v>
+        <v>0.244113</v>
       </c>
       <c r="D30" t="n">
-        <v>5.1337</v>
+        <v>4.9579</v>
       </c>
       <c r="E30" t="n">
-        <v>0.294811</v>
+        <v>0.34211</v>
       </c>
       <c r="F30" t="n">
-        <v>4.023</v>
+        <v>3.8288</v>
       </c>
       <c r="G30" t="n">
-        <v>0.283961</v>
+        <v>0.329518</v>
       </c>
       <c r="H30" t="n">
-        <v>4.1463</v>
+        <v>3.9543</v>
       </c>
       <c r="I30" t="n">
-        <v>0.283961</v>
+        <v>0.329518</v>
       </c>
       <c r="J30" t="n">
-        <v>4.1463</v>
+        <v>3.9543</v>
       </c>
       <c r="K30" t="n">
-        <v>0.155845</v>
+        <v>0.180844</v>
       </c>
       <c r="L30" t="n">
-        <v>6.1219</v>
+        <v>5.9625</v>
       </c>
       <c r="M30" t="n">
-        <v>0.210998</v>
+        <v>0.244847</v>
       </c>
       <c r="N30" t="n">
-        <v>5.1238</v>
+        <v>4.9479</v>
       </c>
       <c r="O30" t="n">
-        <v>0.209736</v>
+        <v>0.243382</v>
       </c>
       <c r="P30" t="n">
-        <v>5.1436</v>
+        <v>4.968</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.44533</v>
+        <v>0.516788</v>
       </c>
       <c r="R30" t="n">
-        <v>2.6668</v>
+        <v>2.4502</v>
       </c>
       <c r="S30" t="n">
-        <v>0.099373</v>
+        <v>0.115311</v>
       </c>
       <c r="T30" t="n">
-        <v>7.6057</v>
+        <v>7.4709</v>
       </c>
       <c r="U30" t="n">
-        <v>0.210366</v>
+        <v>0.244113</v>
       </c>
       <c r="V30" t="n">
-        <v>5.1337</v>
+        <v>4.9579</v>
       </c>
       <c r="W30" t="n">
-        <v>0.210366</v>
+        <v>0.244113</v>
       </c>
       <c r="X30" t="n">
-        <v>5.1337</v>
+        <v>4.9579</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.140312</v>
+        <v>0.162818</v>
       </c>
       <c r="Z30" t="n">
-        <v>6.4679</v>
+        <v>6.3143</v>
       </c>
     </row>
   </sheetData>
@@ -8083,40 +8083,40 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.823</v>
+        <v>3.7828</v>
       </c>
       <c r="E2" t="n">
-        <v>8.3186</v>
+        <v>6.2752</v>
       </c>
       <c r="F2" t="n">
-        <v>4.8186</v>
+        <v>2.78</v>
       </c>
       <c r="G2" t="n">
-        <v>4.8186</v>
+        <v>2.78</v>
       </c>
       <c r="H2" t="n">
-        <v>6.8283</v>
+        <v>4.7863</v>
       </c>
       <c r="I2" t="n">
-        <v>5.813</v>
+        <v>3.7727</v>
       </c>
       <c r="J2" t="n">
-        <v>5.8331</v>
+        <v>3.7928</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3135</v>
+        <v>1.2775</v>
       </c>
       <c r="L2" t="n">
-        <v>8.3378</v>
+        <v>6.2933</v>
       </c>
       <c r="M2" t="n">
-        <v>2.5962</v>
+        <v>0.5605</v>
       </c>
       <c r="N2" t="n">
-        <v>9.0585</v>
+        <v>7.0137</v>
       </c>
       <c r="O2" t="n">
-        <v>3.8347</v>
+        <v>1.7968</v>
       </c>
     </row>
     <row r="3">
@@ -8236,40 +8236,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5.8198</v>
+        <v>3.8709</v>
       </c>
       <c r="E5" t="n">
-        <v>7.2336</v>
+        <v>5.2816</v>
       </c>
       <c r="F5" t="n">
-        <v>4.8154</v>
+        <v>2.8681</v>
       </c>
       <c r="G5" t="n">
-        <v>4.8154</v>
+        <v>2.8681</v>
       </c>
       <c r="H5" t="n">
-        <v>6.8251</v>
+        <v>4.8745</v>
       </c>
       <c r="I5" t="n">
-        <v>5.8098</v>
+        <v>3.8609</v>
       </c>
       <c r="J5" t="n">
-        <v>5.8299</v>
+        <v>3.8809</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3103</v>
+        <v>1.3654</v>
       </c>
       <c r="L5" t="n">
-        <v>8.3346</v>
+        <v>6.3816</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5539</v>
+        <v>1.6094</v>
       </c>
       <c r="N5" t="n">
-        <v>8.09</v>
+        <v>6.1367</v>
       </c>
       <c r="O5" t="n">
-        <v>4.8277</v>
+        <v>2.8812</v>
       </c>
     </row>
     <row r="6">
@@ -8389,40 +8389,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5.6234</v>
+        <v>3.9004</v>
       </c>
       <c r="E8" t="n">
-        <v>5.8433</v>
+        <v>4.1252</v>
       </c>
       <c r="F8" t="n">
-        <v>4.6191</v>
+        <v>2.8976</v>
       </c>
       <c r="G8" t="n">
-        <v>4.6191</v>
+        <v>2.8976</v>
       </c>
       <c r="H8" t="n">
-        <v>6.6285</v>
+        <v>4.9041</v>
       </c>
       <c r="I8" t="n">
-        <v>5.6133</v>
+        <v>3.8904</v>
       </c>
       <c r="J8" t="n">
-        <v>5.6334</v>
+        <v>3.9104</v>
       </c>
       <c r="K8" t="n">
-        <v>3.1143</v>
+        <v>1.3949</v>
       </c>
       <c r="L8" t="n">
-        <v>8.137700000000001</v>
+        <v>6.4111</v>
       </c>
       <c r="M8" t="n">
-        <v>4.42</v>
+        <v>2.6941</v>
       </c>
       <c r="N8" t="n">
-        <v>6.828</v>
+        <v>5.1079</v>
       </c>
       <c r="O8" t="n">
-        <v>5.7327</v>
+        <v>4.0048</v>
       </c>
     </row>
     <row r="9">
@@ -8542,40 +8542,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5.1879</v>
+        <v>3.8774</v>
       </c>
       <c r="E11" t="n">
-        <v>4.1224</v>
+        <v>2.813</v>
       </c>
       <c r="F11" t="n">
-        <v>4.184</v>
+        <v>2.8746</v>
       </c>
       <c r="G11" t="n">
-        <v>4.184</v>
+        <v>2.8746</v>
       </c>
       <c r="H11" t="n">
-        <v>6.1927</v>
+        <v>4.881</v>
       </c>
       <c r="I11" t="n">
-        <v>5.1779</v>
+        <v>3.8673</v>
       </c>
       <c r="J11" t="n">
-        <v>5.198</v>
+        <v>3.8874</v>
       </c>
       <c r="K11" t="n">
-        <v>2.6797</v>
+        <v>1.3719</v>
       </c>
       <c r="L11" t="n">
-        <v>7.7014</v>
+        <v>6.3881</v>
       </c>
       <c r="M11" t="n">
-        <v>5.131</v>
+        <v>3.8205</v>
       </c>
       <c r="N11" t="n">
-        <v>5.2449</v>
+        <v>3.9343</v>
       </c>
       <c r="O11" t="n">
-        <v>6.4855</v>
+        <v>5.1735</v>
       </c>
     </row>
     <row r="12">
@@ -8695,40 +8695,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5.1643</v>
+        <v>4.0457</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5028</v>
+        <v>2.3857</v>
       </c>
       <c r="F14" t="n">
-        <v>4.1604</v>
+        <v>3.0428</v>
       </c>
       <c r="G14" t="n">
-        <v>4.1604</v>
+        <v>3.0428</v>
       </c>
       <c r="H14" t="n">
-        <v>6.169</v>
+        <v>5.0495</v>
       </c>
       <c r="I14" t="n">
-        <v>5.1542</v>
+        <v>4.0357</v>
       </c>
       <c r="J14" t="n">
-        <v>5.1743</v>
+        <v>4.0558</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6561</v>
+        <v>1.5399</v>
       </c>
       <c r="L14" t="n">
-        <v>7.6776</v>
+        <v>6.5568</v>
       </c>
       <c r="M14" t="n">
-        <v>5.6394</v>
+        <v>4.5205</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6892</v>
+        <v>3.5711</v>
       </c>
       <c r="O14" t="n">
-        <v>7.0135</v>
+        <v>5.8934</v>
       </c>
     </row>
     <row r="15">
@@ -8848,40 +8848,40 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5.1923</v>
+        <v>3.9721</v>
       </c>
       <c r="E17" t="n">
-        <v>3.9534</v>
+        <v>2.7344</v>
       </c>
       <c r="F17" t="n">
-        <v>4.1884</v>
+        <v>2.9692</v>
       </c>
       <c r="G17" t="n">
-        <v>4.1884</v>
+        <v>2.9692</v>
       </c>
       <c r="H17" t="n">
-        <v>6.197</v>
+        <v>4.9758</v>
       </c>
       <c r="I17" t="n">
-        <v>5.1822</v>
+        <v>3.962</v>
       </c>
       <c r="J17" t="n">
-        <v>5.2023</v>
+        <v>3.9821</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6841</v>
+        <v>1.4664</v>
       </c>
       <c r="L17" t="n">
-        <v>7.7057</v>
+        <v>6.483</v>
       </c>
       <c r="M17" t="n">
-        <v>5.2901</v>
+        <v>4.0698</v>
       </c>
       <c r="N17" t="n">
-        <v>5.0945</v>
+        <v>3.8744</v>
       </c>
       <c r="O17" t="n">
-        <v>6.6503</v>
+        <v>5.4286</v>
       </c>
     </row>
     <row r="18">
@@ -9001,40 +9001,40 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5.2122</v>
+        <v>4.6102</v>
       </c>
       <c r="E20" t="n">
-        <v>4.0811</v>
+        <v>3.4797</v>
       </c>
       <c r="F20" t="n">
-        <v>4.2082</v>
+        <v>3.6068</v>
       </c>
       <c r="G20" t="n">
-        <v>4.2082</v>
+        <v>3.6068</v>
       </c>
       <c r="H20" t="n">
-        <v>6.2169</v>
+        <v>5.6144</v>
       </c>
       <c r="I20" t="n">
-        <v>5.2021</v>
+        <v>4.6002</v>
       </c>
       <c r="J20" t="n">
-        <v>5.2222</v>
+        <v>4.6202</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7039</v>
+        <v>2.1032</v>
       </c>
       <c r="L20" t="n">
-        <v>7.7257</v>
+        <v>7.1224</v>
       </c>
       <c r="M20" t="n">
-        <v>5.2137</v>
+        <v>4.6117</v>
       </c>
       <c r="N20" t="n">
-        <v>5.2107</v>
+        <v>4.6087</v>
       </c>
       <c r="O20" t="n">
-        <v>6.5703</v>
+        <v>5.9677</v>
       </c>
     </row>
     <row r="21">
@@ -9154,40 +9154,40 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5.2198</v>
+        <v>5.0173</v>
       </c>
       <c r="E23" t="n">
-        <v>4.0904</v>
+        <v>3.8881</v>
       </c>
       <c r="F23" t="n">
-        <v>4.2158</v>
+        <v>4.0135</v>
       </c>
       <c r="G23" t="n">
-        <v>4.2158</v>
+        <v>4.0135</v>
       </c>
       <c r="H23" t="n">
-        <v>6.2245</v>
+        <v>6.0219</v>
       </c>
       <c r="I23" t="n">
-        <v>5.2097</v>
+        <v>5.0072</v>
       </c>
       <c r="J23" t="n">
-        <v>5.2298</v>
+        <v>5.0273</v>
       </c>
       <c r="K23" t="n">
-        <v>2.7115</v>
+        <v>2.5094</v>
       </c>
       <c r="L23" t="n">
-        <v>7.7332</v>
+        <v>7.5303</v>
       </c>
       <c r="M23" t="n">
-        <v>5.2198</v>
+        <v>5.0173</v>
       </c>
       <c r="N23" t="n">
-        <v>5.2198</v>
+        <v>5.0173</v>
       </c>
       <c r="O23" t="n">
-        <v>6.5764</v>
+        <v>6.3736</v>
       </c>
     </row>
     <row r="24">
